--- a/auditoria/auditoria_dados_es.xlsx
+++ b/auditoria/auditoria_dados_es.xlsx
@@ -21,10 +21,11 @@
     <sheet name="10_Trajetoria" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="11_Camada2015" sheetId="12" state="visible" r:id="rId14"/>
     <sheet name="12_Verificacao" sheetId="13" state="visible" r:id="rId15"/>
-    <sheet name="13_Integridade" sheetId="14" state="visible" r:id="rId16"/>
-    <sheet name="14_Referencias" sheetId="15" state="visible" r:id="rId17"/>
-    <sheet name="15_Defeitos" sheetId="16" state="visible" r:id="rId18"/>
-    <sheet name="16_Proveniencia" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="13_Metodo" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="14_Integridade" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="15_Referencias" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="16_Defeitos" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="17_Proveniencia" sheetId="18" state="visible" r:id="rId20"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="832">
   <si>
     <t xml:space="preserve">Auditoria dos dados do artigo</t>
   </si>
@@ -167,25 +168,31 @@
     <t xml:space="preserve">Verificação número-a-número: artigo ↔ fonte, com recomputação viva</t>
   </si>
   <si>
-    <t xml:space="preserve">13_Integridade</t>
+    <t xml:space="preserve">13_Metodo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auditoria metodológica: o indicador sustenta o que a frase afirma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14_Integridade</t>
   </si>
   <si>
     <t xml:space="preserve">Integridade contábil e reprodutibilidade</t>
   </si>
   <si>
-    <t xml:space="preserve">14_Referencias</t>
+    <t xml:space="preserve">15_Referencias</t>
   </si>
   <si>
     <t xml:space="preserve">Integridade das referências bibliográficas</t>
   </si>
   <si>
-    <t xml:space="preserve">15_Defeitos</t>
+    <t xml:space="preserve">16_Defeitos</t>
   </si>
   <si>
     <t xml:space="preserve">Defeitos encontrados na auditoria e status das correções</t>
   </si>
   <si>
-    <t xml:space="preserve">16_Proveniencia</t>
+    <t xml:space="preserve">17_Proveniencia</t>
   </si>
   <si>
     <t xml:space="preserve">Mapa script → output → o que computa</t>
@@ -1349,7 +1356,739 @@
     <t xml:space="preserve">04_Cluster · linha do ES (a introdução arredonda para 'cerca de 2%')</t>
   </si>
   <si>
-    <t xml:space="preserve">Resumo: 41 afirmações verificadas. Os desvios remanescentes são de arredondamento — o artigo publica 1 ou 2 casas decimais, e alguns números convivem em duas agregações (bi-regional × interestadual), conciliadas no Apêndice B.2 do artigo.</t>
+    <t xml:space="preserve">Mineração — ligação para frente (texto: ≈1,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02_Multiplicadores · coluna J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mineração — ligação para trás (texto: ≈0,9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02_Multiplicadores · coluna I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grau de integração — CV da ligação para trás</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02_Multiplicadores · STDEVP÷AVERAGE (CV populacional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grau de integração — CV da ligação para frente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ligação pura × VBP — correlação de Pearson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02_Multiplicadores · CORREL(PTL;VBP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resumo: 47 afirmações verificadas. Os desvios remanescentes são de arredondamento — o artigo publica 1 ou 2 casas decimais, e alguns números convivem em duas agregações (bi-regional × interestadual), conciliadas no Apêndice B.2 do artigo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auditoria metodológica das afirmações numéricas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A aba 12 pergunta se o número publicado bate com o CSV; esta pergunta se o indicador usado sustenta o que a frase afirma — são coisas diferentes. Os critérios saem do protocolo que o repositório já pratica (AUDITORIA.md B1–B6, AUDITORIA_HARD.md §0–§5, os gates INTEGRITY, os achados F1–F8 do parecer matemático); quatro são externos, acrescentados porque o protocolo interno não os cobre, e vêm marcados como tal na coluna Origem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  30 das 47 afirmações passam sem ressalva; 14 têm ressalva declarada longe do número; 3 pedem revisão.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Nenhum achado corrompe número publicado. O de maior consequência é o M — teste prometido em nota de rodapé e nunca executado, pela regra do próprio repositório.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloco 1 — critérios do crivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Código</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Critério</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Origem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veredito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como o artigo se posiciona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identidade contábil x = Z1 + y e aditividade exata da decomposição</t>
+  </si>
+  <si>
+    <t xml:space="preserve">interno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUDITORIA.md:6 · 25_decomposicao_fd.py:74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✓ ADEQUADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assert de aditividade no próprio script; erro máximo de 0,00% registrado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hawkins-Simon: soma de coluna de A &lt; 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUDITORIA.md:7 · RESULTADOS_RQ_AB.md:103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,748 bi-regional e 0,895 interestadual; a exceção do S23 (1,07) é declarada e testada por sensibilidade no Apêndice B.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inversa de Leontief não negativa: B = (I−A)⁻¹ ≥ 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUDITORIA.md:7 · 01_es_br_base.py:122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verificado em todos os sistemas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiplicadores ≥ 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLANO_ARTIGO.md:49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o mínimo publicado é 1,15 (serviços imobiliários), na Tabela 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ligação para frente pela inversa de Ghosh, não por soma de linha de Leontief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUDITORIA.md:16 · src/io_core.py:127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o Apêndice A.4 declara G = (I−F)⁻¹ com F = x̂⁻¹Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O modelo de Ghosh é oferta-dirigido: a ligação para frente vale como métrica de posição, não como previsão de impacto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXTERNO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oosterhaven (1988); Dietzenbacher (1997) — ausente em todo o repositório</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚑ REVISAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o artigo diz 'pelo lado da oferta' (§3 e Apêndice A.4), mas em nenhum ponto registra que a leitura causal do modelo é contestada. Ver achado N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipo II é limite inferior do induzido local</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVIEW_THEORIST_TOOLBOX.md:55 (F6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o Apêndice A.1 traz o argumento de monotonicidade pela série de Neumann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duas agregações legítimas do mesmo fluxo exigem nota de reconciliação, nunca escolha silenciosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUDITORIA.md:58 · REVIEW_CARACTERIZACAO.md:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quatro precedentes no repo; o Apêndice B.2 concilia 24,9 / 22,9 / 22,8 / 27,4 e a nota da Tabela 5 concilia 90,9 com 91,6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preços correntes: oscilação anual em setor sensível a preço é efeito nominal, não estrutural</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESULTADOS_CARACTERIZACAO.md:151 · DEEP_RESEARCH_PANORAMA.md:81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">declarado na Limitação (ii) E no ponto de uso, no parágrafo da siderurgia em §5. A deflação da série segue pendente como agenda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CILQ sem correção FLQ subestima o vazamento: o valor é limite inferior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVISAO_LITERATURA_IIOAS.md:63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~ RESSALVA FORA DO PONTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">declarado na Limitação (iii) como 'ordens de grandeza', mas não no ponto dos LQ de 2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A conclusão precisa ser invariante à convenção de spillover/feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_reconciliacao.py:70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o Apêndice B.3 reporta a banda 0,15–0,32% em quatro convenções alternativas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extração hipotética: declarar a especificação da injeção no ponto do número</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVIEW_FULL_MODE_V2.md:102 (R1-W3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o Apêndice A.7 declara que a injeção é a demanda final intra-estadual; o §6, onde os 13,0% aparecem, não repete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ligações puras são largamente tamanho: reportar junto com Rasmussen-Hirschman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17_caracterizacao_es_2008.py:88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nota de rodapé no §4 com o Pearson 0,96, agora auditável na aba 02 pela coluna VBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modelo nulo é ajuste descritivo, sem pretensão inferencial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVIEW_THEORIST_TOOLBOX.md:67 (F8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n/a nesta revisão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o apêndice de escores-z saiu da revisão final; nenhuma afirmação auditada depende dele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cruzamento entre safras e agregações exige rótulo explícito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEEP_RESEARCH_PANORAMA.md:264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 / 35 / 68 setores e as safras 2008 / 2015 / 2010–2021 são declarados em §3.1 e nas Limitações (ii) e (iii)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todo número publicado precisa de artefato persistido, não de stdout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVIEW_THEORIST_TOOLBOX.md:42 (F4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">falha em um caso: a decomposição de Miyazawa do Apêndice A.3 não é computada por nenhum script. Ver achado L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teste prometido e não rodado conta como teste falhando</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVIEW_THEORIST_TOOLBOX.md:14 (F1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">falha em um caso: a reestimação do ranking de base sem Alimentos é prometida em nota de rodapé no §4 e nunca foi executada. Ver achado M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentuais calculados sobre os valores, não soma de parcelas arredondadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">esta pasta, aba 03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">corrigido nesta edição: somar a coluna de % do CSV dava um TOTAL de 100,01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O CSV persistido precisa ser internamente coerente em unidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">falha: es_caracterizacao_2008.csv traz a mesma grandeza em duas unidades na mesma linha. Ver achado J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cruzamento de escalas exige tabela-ponte de concordância</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a ponte 26↔35↔68 nunca foi construída; o artigo supre rotulando a comparação inter-escala como qualitativa, o que atende ao espírito da regra sem cumpri-la</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A guarda de Hawkins-Simon deve ser uniforme entre escalas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14_benchmark_ufs.py:42 vs 18_trajetoria_n68.py:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">falha: um script usa assert, o outro detecta a violação e faz pass. Ver achado K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A convenção do coeficiente de variação deve ser declarada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o CV publicado (0,16 / 0,28) é o populacional; o amostral daria 0,17 / 0,29. A escolha não está no texto. Ver achado S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloco 2 — as afirmações, uma a uma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Critérios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicador usado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ressalva ou redação sugerida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">média simples entre 26 setores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">média ponderada pelo VBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">as duas médias aparecem na mesma frase do §7 e no Apêndice B.2 — é o precedente do repo cumprido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valor setorial direto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M4 · M8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">média simples, bi-regional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">média simples, fechamento tipo II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M8 · M19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o número publicado está certo, mas a coluna mult_emp_I do CSV está gravada ×1e6 e a coluna emp_dir_Rmi da mesma linha, não. Quem replicar pelo artefato erra por seis ordens de grandeza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M7 · M19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">média simples, tipo II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mesma incoerência de unidade no artefato (achado J)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTL padronizada pela média dos 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a nota do §4 declara o Pearson 0,96 no ponto de uso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTL padronizada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1 · M18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soma de dois componentes de y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total da decomposição</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parcela do VBP nos setores rotulados base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o rótulo inclui Alimentos (22_benchmark_caracterizacao.py:18) e a nota de rodapé do §4 promete a reestimação sem Alimentos 'como checagem de replicação'. Enquanto ela não rodar, o '2º mais intensivo' é condicional ao rótulo. Redação sugerida: '2º mais intensivo em setores de base sob a classificação adotada, que inclui Alimentos'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M8 · M15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">média ponderada, interestadual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a nota de rodapé do §4 reconcilia com o 1,76 da média simples bi-regional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M5 · M15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ligação de Leontief ponderada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">razão sobre o setor dominante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">não depende do rótulo base: o setor dominante é determinado por porte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mediana entre 27 UFs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a mediana é calculada sobre a mesma coluna rotulada; herda a condicionalidade do achado M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soma de parcelas de destino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">razão da inversa particionada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o Apêndice B.3 mostra a invariância à convenção (0,15–0,32%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">razão das somas ponderadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a nota da Tabela 5 distingue da média ponderada das razões (91,6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parcela do VBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M12 · M16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">extração hipotética</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a especificação da injeção (demanda final intra-estadual) está só no Apêndice A.7. Redação sugerida no §6: '...cairia 13,0% sob a injeção da demanda final intra-estadual'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M10 · M20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quociente locacional, 2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o LQ de 2015 vem da regionalização CILQ sem correção FLQ; a ressalva está na Limitação (iii)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">idem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">além da ressalva do CILQ: o texto diz 'rochas ornamentais' e o dado é 'Minerais não-metálicos'. Ver achado T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M9 · M15 · M21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ligação de Leontief, série nacional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preços correntes (Limitação ii) e o script do panorama detecta violação de Hawkins-Simon sem agir (achado K). A tendência de 12 anos é robusta ao efeito nominal; o nível de um ano, não</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M9 · M21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">multiplicador, série nacional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parcela do valor adicionado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a Tabela 3 publica 2,2 e a introdução arredonda para 'cerca de 2%' — as duas leituras do mesmo 2,15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M5 · M6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ligação de Ghosh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o número confere, mas sustenta a leitura de 'fornecedora a montante'. Por M6, a ligação de Ghosh mede posição, não impacto — a frase do §4 não deve ser lida como previsão de efeito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ligação de Leontief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CV populacional das ligações</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o CV é o populacional; declarar qual, já que o amostral daria 0,17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M6 · M22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">idem, e a ligação a frente é de Ghosh (M6): o amostral daria 0,29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M13 · M16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pearson entre PTL e VBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agora auditável por fórmula na aba 02; antes só existia como print de console</t>
+  </si>
+  <si>
+    <t xml:space="preserve">razão sobre a injeção declarada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloco 3 — achados (a série A–I está na aba 16)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Severidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Categoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Afeta número publicado?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correção sugerida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">es_caracterizacao_2008.csv grava mult_emp_I multiplicado por 1e6 (46.669.630,07) enquanto emp_dir_Rmi e emp_ind_Rmi, na mesma linha, somam 46,67. A mesma grandeza em duas unidades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🟠 Médio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reproducibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não — os números publicados dividem por 1e6 corretamente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gravar já por R$ 1 milhão, ou renomear a coluna para explicitar o fator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABERTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18_trajetoria_n68.py:56-58 detecta soma de coluna de A ≥ 1 e executa pass; 14_benchmark_ufs.py:42 usa assert para a mesma checagem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indeterminado — UNVERIFIABLE_ACCESS: as matrizes do Nível 68 não estão no repositório, não é possível saber se a violação dispara em algum ano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trocar pass por assert, ou registrar em CSV quais anos violam e o raio espectral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A decomposição de Miyazawa do Apêndice A.3 não é computada por nenhum script (varredura em *.py: zero ocorrências); a cadeia número→artefato fecha por identidade algébrica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não — o valor é o feedback já verificado, por identidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ou um script que compute Δ_LL e persista o CSV, ou uma frase no apêndice dizendo que o resultado é identidade algébrica e não cálculo independente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A reestimação do ranking de base excluindo Alimentos é prometida em nota de rodapé no §4 'como checagem de replicação' e nunca foi executada (DA-1, aberto desde a rodada 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">research-integrity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sim, condicionalmente — o '2º mais intensivo em base' (36,4%) e a mediana de 21,0 dependem do rótulo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rodar 22_* e 10_* sem Alimentos e reportar o novo ranking, ou retirar a promessa da nota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nenhum documento do repositório registra a crítica canônica ao modelo de Ghosh como oferta-dirigido; Ghosh entra apenas como 'a convenção correta' para a ligação a frente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">causal-identification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não — nenhum número muda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meia frase no Apêndice A.4: a ligação a frente por Ghosh mede posição na cadeia, e a leitura do modelo como oferta-dirigido é contestada na literatura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duas referências de proveniência desta pasta apontavam para lugares inexistentes: 'AUDITORIA.md §B7' (seção nunca escrita) e uma nota CILQ em dados/README.md (25 linhas, não a contém)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🟡 Menor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">citation-hygiene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reapontadas para AUDITORIA.md B1–B6 e RESULTADOS_RQ_AB.md:103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APLICADO nesta edição</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">src/io_core.py não é importado por nenhum script (zero imports), mas README.md:47 e dados/README.md:11 o apresentam como funções-núcleo usadas pelo pipeline. Cobre parte da bateria: sem tipo II, ligações puras, extração hipotética, Miyazawa, LQ/HHI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrigir os dois README, ou passar a importá-lo de fato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dados/README.md descreve o pipeline como '01–13' quando o artigo depende de 14 a 27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atualizar a faixa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O protocolo B7 é invocado pelo nome e usado, mas nunca foi definido em nenhum .md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escrever B7 em AUDITORIA.md: verificação de metadados das referências que sustentam números, com o vocabulário VERIFICADA / CORRIGIDA / UNVERIFIABLE_ACCESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O coeficiente de variação publicado (0,16 / 0,28) é o populacional; o amostral daria 0,17 / 0,29. A convenção não está declarada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🟢 Cosmético</t>
+  </si>
+  <si>
+    <t xml:space="preserve">writing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uma palavra no Apêndice A.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O texto diz 'rochas ornamentais no Central Sul' e o setor correspondente no dado é 'Minerais não-metálicos' (LQ 7,687)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nota de equivalência — já registrada na aba 09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tensão no cânone interno: DEEP_RESEARCH_CARACTERIZACAO.md:60 diz que as ligações puras corrigem o viés de Rasmussen-Hirschman por não pesar tamanho; a Limitação (iv) diz que elas favorecem setores grandes. As duas leituras são defensáveis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🟢 Declarado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nenhuma ação necessária; registrado para o caso de o parecerista notar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24_micro_mult_chave.py e 25_decomposicao_fd.py declaram em docstring ser reconstrução de um original não versionado a tempo; alimentam a Tabela 5 e a Tabela 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não — a autoverificação de ambos bate com os valores publicados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nenhuma, além de manter a autoverificação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">declarado/transparente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seis números publicados não tinham linha de verificação: as ligações ≈1,2 e ≈0,9 da mineração, os dois coeficientes de variação, o Pearson 0,96 e os 35% da injeção</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seis linhas acrescentadas à aba 12</t>
   </si>
   <si>
     <t xml:space="preserve">Fontes: pesquisa/AUDITORIA.md (B1–B5) e pesquisa/AUDITORIA_HARD.md (§0, §3).</t>
@@ -1451,9 +2190,6 @@
     <t xml:space="preserve">Detalhe bibliográfico</t>
   </si>
   <si>
-    <t xml:space="preserve">Veredito</t>
-  </si>
-  <si>
     <t xml:space="preserve">Guilhoto &amp; Sesso Filho (2005)</t>
   </si>
   <si>
@@ -1523,12 +2259,6 @@
     <t xml:space="preserve">Fonte: pesquisa/AUDITORIA_HARD.md §2 e §5. Nenhum defeito corrompe número publicado. Os itens B e E dizem respeito à camada de upstreamness/WIOD, que a revisão final do artigo abandonou — ficam registrados como histórico do processo.</t>
   </si>
   <si>
-    <t xml:space="preserve">ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Severidade</t>
-  </si>
-  <si>
     <t xml:space="preserve">A</t>
   </si>
   <si>
@@ -1544,9 +2274,6 @@
     <t xml:space="preserve">B</t>
   </si>
   <si>
-    <t xml:space="preserve">🟠 Médio</t>
-  </si>
-  <si>
     <t xml:space="preserve">WIOD (Timmer 2015) na bibliografia mas nunca citado no corpo, sendo a fonte de toda a camada de upstreamness</t>
   </si>
   <si>
@@ -1574,9 +2301,6 @@
     <t xml:space="preserve">E</t>
   </si>
   <si>
-    <t xml:space="preserve">🟡 Menor</t>
-  </si>
-  <si>
     <t xml:space="preserve">Distribuição global do WIOD contaminada (49/2464 com demanda final &lt; 0)</t>
   </si>
   <si>
@@ -1592,9 +2316,6 @@
     <t xml:space="preserve">G</t>
   </si>
   <si>
-    <t xml:space="preserve">🟢 Cosmético</t>
-  </si>
-  <si>
     <t xml:space="preserve">Arredondamentos/rótulos: spillover 18,1 (Sankey) vs 18,2; 65 vs 65,4; 61,7 vs 61,8 na soma das parcelas</t>
   </si>
   <si>
@@ -1604,13 +2325,7 @@
     <t xml:space="preserve">H</t>
   </si>
   <si>
-    <t xml:space="preserve">🟢 Declarado</t>
-  </si>
-  <si>
     <t xml:space="preserve">Escolhas de definição: 'base/commodity' inclui Alimentos; PIB por valor adicionado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">declarado/transparente</t>
   </si>
   <si>
     <t xml:space="preserve">I</t>
@@ -2500,7 +3215,7 @@
     <tabColor rgb="FFB7B5AC"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:C39"/>
+  <dimension ref="B1:C40"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="1.2"/>
@@ -2720,41 +3435,49 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="5" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="8" t="s">
         <v>51</v>
       </c>
+      <c r="C33" s="9" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C36" s="13" t="s">
+      <c r="B36" s="5" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="14" t="s">
-        <v>52</v>
+      <c r="B37" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="C37" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="14" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="15" t="s">
-        <v>52</v>
-      </c>
       <c r="C38" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="16" t="s">
-        <v>52</v>
+      <c r="B39" s="15" t="s">
+        <v>54</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -2789,12 +3512,12 @@
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="17" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
@@ -2809,12 +3532,12 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -2829,7 +3552,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -2844,42 +3567,42 @@
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="19" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D9" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="E9" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="F9" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="H9" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="I9" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="J9" s="19" t="s">
         <v>251</v>
       </c>
-      <c r="G9" s="19" t="s">
-        <v>245</v>
-      </c>
-      <c r="H9" s="19" t="s">
+      <c r="K9" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="L9" s="19" t="s">
         <v>255</v>
-      </c>
-      <c r="I9" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="J9" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="K9" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="L9" s="19" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="20" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C10" s="21" t="n">
         <v>0.039</v>
@@ -2914,7 +3637,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="24" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C11" s="25" t="n">
         <v>0.049</v>
@@ -2949,7 +3672,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="20" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C12" s="21" t="n">
         <v>0.356</v>
@@ -2984,7 +3707,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="24" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C13" s="25" t="n">
         <v>0.183</v>
@@ -3019,7 +3742,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="20" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C14" s="21" t="n">
         <v>1.192</v>
@@ -3054,7 +3777,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="24" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C15" s="25" t="n">
         <v>0.977</v>
@@ -3089,7 +3812,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="20" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C16" s="21" t="n">
         <v>0.764</v>
@@ -3124,7 +3847,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="24" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C17" s="25" t="n">
         <v>0.581</v>
@@ -3159,7 +3882,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="20" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C18" s="21" t="n">
         <v>0.524</v>
@@ -3194,7 +3917,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="24" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C19" s="25" t="n">
         <v>0.177</v>
@@ -3229,7 +3952,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="20" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C20" s="21" t="n">
         <v>0.67</v>
@@ -3264,7 +3987,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="24" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C21" s="25" t="n">
         <v>1.356</v>
@@ -3299,7 +4022,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C22" s="21" t="n">
         <v>0.444</v>
@@ -3334,7 +4057,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="24" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C23" s="25" t="n">
         <v>1.556</v>
@@ -3369,7 +4092,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C24" s="21" t="n">
         <v>0.788</v>
@@ -3404,7 +4127,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="24" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C25" s="25" t="n">
         <v>0.192</v>
@@ -3439,7 +4162,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="20" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C26" s="21" t="n">
         <v>0.785</v>
@@ -3474,7 +4197,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C27" s="25" t="n">
         <v>1.037</v>
@@ -3509,7 +4232,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="20" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C28" s="21" t="n">
         <v>1.133</v>
@@ -3544,7 +4267,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="24" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C29" s="25" t="n">
         <v>1.04</v>
@@ -3579,7 +4302,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="20" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C30" s="21" t="n">
         <v>1.29</v>
@@ -3614,7 +4337,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="24" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C31" s="25" t="n">
         <v>1.08</v>
@@ -3649,7 +4372,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="20" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C32" s="21" t="n">
         <v>1.079</v>
@@ -3684,7 +4407,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="24" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C33" s="25" t="n">
         <v>1.026</v>
@@ -3719,7 +4442,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="20" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C34" s="21" t="n">
         <v>1.035</v>
@@ -3754,7 +4477,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="24" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C35" s="25" t="n">
         <v>1.213</v>
@@ -3789,7 +4512,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="20" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C36" s="21" t="n">
         <v>1.174</v>
@@ -3824,7 +4547,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="24" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C37" s="25" t="n">
         <v>1.031</v>
@@ -3859,7 +4582,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="20" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C38" s="21" t="n">
         <v>0.901</v>
@@ -3894,7 +4617,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="24" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C39" s="25" t="n">
         <v>1.033</v>
@@ -3929,7 +4652,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="20" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C40" s="21" t="n">
         <v>1.157</v>
@@ -3964,7 +4687,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="24" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C41" s="25" t="n">
         <v>1.02</v>
@@ -3999,7 +4722,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="20" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C42" s="21" t="n">
         <v>1.16</v>
@@ -4034,7 +4757,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="24" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C43" s="25" t="n">
         <v>1.118</v>
@@ -4069,7 +4792,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="20" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C44" s="21" t="n">
         <v>0.945</v>
@@ -4134,12 +4857,12 @@
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="17" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
@@ -4156,12 +4879,12 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -4178,7 +4901,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -4195,48 +4918,48 @@
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="19" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J9" s="19" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L9" s="19" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M9" s="19" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N9" s="19" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="20" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C10" s="21" t="n">
         <v>1.4073</v>
@@ -4277,7 +5000,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="24" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C11" s="25" t="n">
         <v>1.3109</v>
@@ -4318,7 +5041,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="20" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C12" s="21" t="n">
         <v>1.1627</v>
@@ -4359,7 +5082,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="24" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C13" s="25" t="n">
         <v>0.829</v>
@@ -4400,7 +5123,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="20" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C14" s="21" t="n">
         <v>0.7998</v>
@@ -4441,48 +5164,48 @@
     </row>
     <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="19" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I17" s="19" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J17" s="19" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K17" s="19" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L17" s="19" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M17" s="19" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N17" s="19" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="20" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C18" s="21" t="n">
         <v>2.8518</v>
@@ -4523,7 +5246,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="24" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C19" s="25" t="n">
         <v>2.6566</v>
@@ -4564,7 +5287,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="20" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C20" s="21" t="n">
         <v>2.3562</v>
@@ -4605,7 +5328,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="24" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C21" s="25" t="n">
         <v>1.68</v>
@@ -4646,7 +5369,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="20" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C22" s="21" t="n">
         <v>1.6209</v>
@@ -4719,122 +5442,122 @@
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="17" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="19" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="20" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D7" s="20"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="24" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="20" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C9" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="D9" s="20" t="s">
         <v>336</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="24" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="20" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="24" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="20" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="24" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -4857,7 +5580,7 @@
     <tabColor rgb="FFB7B5AC"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:H52"/>
+  <dimension ref="B1:H58"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="1.2"/>
@@ -4873,12 +5596,12 @@
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="17" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
@@ -4889,12 +5612,12 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -4905,7 +5628,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -4916,39 +5639,39 @@
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="19" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="32" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D10" s="21" t="n">
         <v>24.9</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F10" s="21" t="n">
         <f aca="false">AVERAGE(01_Setores!F10:F35)</f>
@@ -4965,16 +5688,16 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="33" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D11" s="25" t="n">
         <v>22.9</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F11" s="25" t="n">
         <f aca="false">SUMPRODUCT(01_Setores!F10:F35,01_Setores!K10:K35)/SUM(01_Setores!K10:K35)</f>
@@ -4991,16 +5714,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="32" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D12" s="21" t="n">
         <v>5.2</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F12" s="21" t="n">
         <f aca="false">INDEX(01_Setores!F10:F35,MATCH("Serviços imobiliários e aluguel",01_Setores!B10:B35,0))</f>
@@ -5017,16 +5740,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="33" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>37.4</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F13" s="25" t="n">
         <f aca="false">INDEX(01_Setores!F10:F35,MATCH("Alimentos, bebidas e fumo",01_Setores!B10:B35,0))</f>
@@ -5043,16 +5766,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="32" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D14" s="21" t="n">
         <v>61.6</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F14" s="21" t="n">
         <f aca="false">INDEX(01_Setores!H10:H35,MATCH("Refino de petróleo, coque e álcool",01_Setores!B10:B35,0))</f>
@@ -5069,16 +5792,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="33" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>49.3</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F15" s="25" t="n">
         <f aca="false">INDEX(01_Setores!H10:H35,MATCH("Metalurgia",01_Setores!B10:B35,0))</f>
@@ -5095,16 +5818,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="32" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D16" s="21" t="n">
         <v>1.76</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F16" s="21" t="n">
         <f aca="false">AVERAGE(02_Multiplicadores!C10:C35)</f>
@@ -5121,16 +5844,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="33" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D17" s="25" t="n">
         <v>2.45</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F17" s="25" t="n">
         <f aca="false">AVERAGE(02_Multiplicadores!D10:D35)</f>
@@ -5147,16 +5870,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="32" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D18" s="21" t="n">
         <v>27.9</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F18" s="21" t="n">
         <f aca="false">AVERAGE(02_Multiplicadores!E10:E35)</f>
@@ -5173,16 +5896,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="33" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D19" s="25" t="n">
         <v>40.4</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F19" s="25" t="n">
         <f aca="false">AVERAGE(02_Multiplicadores!F10:F35)</f>
@@ -5199,16 +5922,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="32" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D20" s="21" t="n">
         <v>4.4</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F20" s="21" t="n">
         <f aca="false">INDEX(02_Multiplicadores!K10:K35,MATCH("Mineração",02_Multiplicadores!B10:B35,0))</f>
@@ -5225,16 +5948,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="33" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D21" s="25" t="n">
         <v>3.4</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F21" s="25" t="n">
         <f aca="false">INDEX(02_Multiplicadores!K10:K35,MATCH("Metalurgia",02_Multiplicadores!B10:B35,0))</f>
@@ -5251,16 +5974,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="32" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D22" s="21" t="n">
         <v>61.7</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F22" s="21" t="n">
         <f aca="false">03_DemandaFinal!D17</f>
@@ -5277,16 +6000,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="33" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D23" s="25" t="n">
         <v>47.5</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F23" s="25" t="n">
         <f aca="false">03_DemandaFinal!F17</f>
@@ -5303,16 +6026,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="32" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D24" s="21" t="n">
         <v>104.6</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F24" s="21" t="n">
         <f aca="false">03_DemandaFinal!C16/1000</f>
@@ -5329,16 +6052,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="33" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D25" s="25" t="n">
         <v>1611.7</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F25" s="25" t="n">
         <f aca="false">03_DemandaFinal!E16/1000</f>
@@ -5355,16 +6078,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D26" s="21" t="n">
         <v>36.4</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F26" s="21" t="n">
         <f aca="false">04_Cluster!F10</f>
@@ -5381,16 +6104,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="33" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D27" s="25" t="n">
         <v>1.66</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F27" s="25" t="n">
         <f aca="false">04_Cluster!G10</f>
@@ -5407,16 +6130,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D28" s="21" t="n">
         <v>25.4</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F28" s="21" t="n">
         <f aca="false">04_Cluster!H10</f>
@@ -5433,16 +6156,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="33" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D29" s="25" t="n">
         <v>0.92</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F29" s="25" t="n">
         <f aca="false">04_Cluster!I10</f>
@@ -5459,16 +6182,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D30" s="21" t="n">
         <v>0.39</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F30" s="21" t="n">
         <f aca="false">04_Cluster!J10</f>
@@ -5485,16 +6208,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="33" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D31" s="25" t="n">
         <v>21</v>
       </c>
       <c r="E31" s="24" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F31" s="25" t="n">
         <f aca="false">05_Estados!H37</f>
@@ -5511,16 +6234,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D32" s="21" t="n">
         <v>42.5</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F32" s="21" t="n">
         <f aca="false">05_Estados!J37</f>
@@ -5537,16 +6260,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="33" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D33" s="25" t="n">
         <v>0.65</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F33" s="25" t="n">
         <f aca="false">05_Estados!L37</f>
@@ -5563,16 +6286,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="32" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D34" s="21" t="n">
         <v>65.4</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F34" s="21" t="n">
         <f aca="false">07_Destino!D36</f>
@@ -5589,16 +6312,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="33" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C35" s="24" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D35" s="25" t="n">
         <v>52.5</v>
       </c>
       <c r="E35" s="24" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F35" s="25" t="n">
         <f aca="false">07_Destino!D37</f>
@@ -5615,16 +6338,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="32" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D36" s="21" t="n">
         <v>0.32</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F36" s="21" t="n">
         <f aca="false">06_Spillover!C15</f>
@@ -5641,16 +6364,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="33" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C37" s="24" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D37" s="25" t="n">
         <v>90.9</v>
       </c>
       <c r="E37" s="24" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F37" s="25" t="n">
         <f aca="false">08_Micro!G10</f>
@@ -5667,16 +6390,16 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="32" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D38" s="21" t="n">
         <v>66.2</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F38" s="21" t="n">
         <f aca="false">08_Micro!G15</f>
@@ -5693,16 +6416,16 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="33" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C39" s="24" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D39" s="25" t="n">
         <v>62.3</v>
       </c>
       <c r="E39" s="24" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F39" s="25" t="n">
         <f aca="false">08_Micro!D10</f>
@@ -5719,16 +6442,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="32" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D40" s="21" t="n">
         <v>13</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F40" s="21" t="n">
         <f aca="false">08_Micro!E24</f>
@@ -5745,16 +6468,16 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="33" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C41" s="24" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D41" s="25" t="n">
         <v>8.2</v>
       </c>
       <c r="E41" s="24" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F41" s="25" t="n">
         <f aca="false">09_Micro_LQ!I19</f>
@@ -5771,16 +6494,16 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="32" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D42" s="21" t="n">
         <v>9.5</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F42" s="21" t="n">
         <f aca="false">09_Micro_LQ!F15</f>
@@ -5797,16 +6520,16 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="33" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C43" s="24" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D43" s="25" t="n">
         <v>9.6</v>
       </c>
       <c r="E43" s="24" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F43" s="25" t="n">
         <f aca="false">09_Micro_LQ!J17</f>
@@ -5823,16 +6546,16 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="32" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D44" s="21" t="n">
         <v>21.9</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F44" s="21" t="n">
         <f aca="false">09_Micro_LQ!D11</f>
@@ -5849,16 +6572,16 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="33" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C45" s="24" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D45" s="25" t="n">
         <v>7.7</v>
       </c>
       <c r="E45" s="24" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F45" s="25" t="n">
         <f aca="false">09_Micro_LQ!G22</f>
@@ -5875,16 +6598,16 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="32" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D46" s="21" t="n">
         <v>1.41</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F46" s="21" t="n">
         <f aca="false">10_Trajetoria!C10</f>
@@ -5901,16 +6624,16 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="33" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C47" s="24" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D47" s="25" t="n">
         <v>1.51</v>
       </c>
       <c r="E47" s="24" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F47" s="25" t="n">
         <f aca="false">10_Trajetoria!N10</f>
@@ -5927,16 +6650,16 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="32" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D48" s="21" t="n">
         <v>2.85</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F48" s="21" t="n">
         <f aca="false">10_Trajetoria!C18</f>
@@ -5953,16 +6676,16 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="33" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C49" s="24" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D49" s="25" t="n">
         <v>3.05</v>
       </c>
       <c r="E49" s="24" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F49" s="25" t="n">
         <f aca="false">10_Trajetoria!N18</f>
@@ -5979,16 +6702,16 @@
     </row>
     <row r="50" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D50" s="21" t="n">
         <v>2.2</v>
       </c>
       <c r="E50" s="20" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F50" s="21" t="n">
         <f aca="false">04_Cluster!D10</f>
@@ -6003,23 +6726,179 @@
         <v>✓</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="47" t="s">
-        <v>437</v>
-      </c>
-      <c r="C52" s="47"/>
-      <c r="D52" s="47"/>
-      <c r="E52" s="47"/>
-      <c r="F52" s="47"/>
-      <c r="G52" s="47"/>
-      <c r="H52" s="47"/>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="33" t="s">
+        <v>383</v>
+      </c>
+      <c r="C51" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="D51" s="25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E51" s="24" t="s">
+        <v>440</v>
+      </c>
+      <c r="F51" s="25" t="n">
+        <f aca="false">INDEX(02_Multiplicadores!J10:J35,MATCH("Mineração",02_Multiplicadores!B10:B35,0))</f>
+        <v>1.2275</v>
+      </c>
+      <c r="G51" s="25" t="n">
+        <f aca="false">F51-D51</f>
+        <v>0.0275000000000001</v>
+      </c>
+      <c r="H51" s="33" t="str">
+        <f aca="false">IF(ABS(ROUND(G51,4))&lt;=0.05,"✓",IF(ABS(ROUND(G51,4))&lt;=0.6,"~","⚑"))</f>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="32" t="s">
+        <v>383</v>
+      </c>
+      <c r="C52" s="20" t="s">
+        <v>441</v>
+      </c>
+      <c r="D52" s="21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E52" s="20" t="s">
+        <v>442</v>
+      </c>
+      <c r="F52" s="21" t="n">
+        <f aca="false">INDEX(02_Multiplicadores!I10:I35,MATCH("Mineração",02_Multiplicadores!B10:B35,0))</f>
+        <v>0.9119</v>
+      </c>
+      <c r="G52" s="21" t="n">
+        <f aca="false">F52-D52</f>
+        <v>0.0119</v>
+      </c>
+      <c r="H52" s="32" t="str">
+        <f aca="false">IF(ABS(ROUND(G52,4))&lt;=0.05,"✓",IF(ABS(ROUND(G52,4))&lt;=0.6,"~","⚑"))</f>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="33" t="s">
+        <v>383</v>
+      </c>
+      <c r="C53" s="24" t="s">
+        <v>443</v>
+      </c>
+      <c r="D53" s="25" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E53" s="24" t="s">
+        <v>444</v>
+      </c>
+      <c r="F53" s="25" t="n">
+        <f aca="false">STDEVP(02_Multiplicadores!I10:I35)/AVERAGE(02_Multiplicadores!I10:I35)</f>
+        <v>0.161952050244177</v>
+      </c>
+      <c r="G53" s="25" t="n">
+        <f aca="false">F53-D53</f>
+        <v>0.00195205024417694</v>
+      </c>
+      <c r="H53" s="33" t="str">
+        <f aca="false">IF(ABS(ROUND(G53,4))&lt;=0.05,"✓",IF(ABS(ROUND(G53,4))&lt;=0.6,"~","⚑"))</f>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="32" t="s">
+        <v>383</v>
+      </c>
+      <c r="C54" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="D54" s="21" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E54" s="20" t="s">
+        <v>444</v>
+      </c>
+      <c r="F54" s="21" t="n">
+        <f aca="false">STDEVP(02_Multiplicadores!J10:J35)/AVERAGE(02_Multiplicadores!J10:J35)</f>
+        <v>0.280305757379625</v>
+      </c>
+      <c r="G54" s="21" t="n">
+        <f aca="false">F54-D54</f>
+        <v>0.000305757379625127</v>
+      </c>
+      <c r="H54" s="32" t="str">
+        <f aca="false">IF(ABS(ROUND(G54,4))&lt;=0.05,"✓",IF(ABS(ROUND(G54,4))&lt;=0.6,"~","⚑"))</f>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="33" t="s">
+        <v>383</v>
+      </c>
+      <c r="C55" s="24" t="s">
+        <v>446</v>
+      </c>
+      <c r="D55" s="25" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E55" s="24" t="s">
+        <v>447</v>
+      </c>
+      <c r="F55" s="25" t="n">
+        <f aca="false">CORREL(02_Multiplicadores!K10:K35,02_Multiplicadores!M10:M35)</f>
+        <v>0.958707654949712</v>
+      </c>
+      <c r="G55" s="25" t="n">
+        <f aca="false">F55-D55</f>
+        <v>-0.00129234505028775</v>
+      </c>
+      <c r="H55" s="33" t="str">
+        <f aca="false">IF(ABS(ROUND(G55,4))&lt;=0.05,"✓",IF(ABS(ROUND(G55,4))&lt;=0.6,"~","⚑"))</f>
+        <v>✓</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="32" t="s">
+        <v>367</v>
+      </c>
+      <c r="C56" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="D56" s="21" t="n">
+        <v>35</v>
+      </c>
+      <c r="E56" s="20" t="s">
+        <v>409</v>
+      </c>
+      <c r="F56" s="21" t="n">
+        <f aca="false">06_Spillover!C16</f>
+        <v>35.2790203805272</v>
+      </c>
+      <c r="G56" s="21" t="n">
+        <f aca="false">F56-D56</f>
+        <v>0.279020380527221</v>
+      </c>
+      <c r="H56" s="32" t="str">
+        <f aca="false">IF(ABS(ROUND(G56,4))&lt;=0.05,"✓",IF(ABS(ROUND(G56,4))&lt;=0.6,"~","⚑"))</f>
+        <v>~</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B58" s="47" t="s">
+        <v>448</v>
+      </c>
+      <c r="C58" s="47"/>
+      <c r="D58" s="47"/>
+      <c r="E58" s="47"/>
+      <c r="F58" s="47"/>
+      <c r="G58" s="47"/>
+      <c r="H58" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B58:H58"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6037,6 +6916,1965 @@
     <tabColor rgb="FFB7B5AC"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B1:H98"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="1.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="18" t="s">
+        <v>451</v>
+      </c>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="18" t="s">
+        <v>452</v>
+      </c>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="5" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>456</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>457</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="32" t="s">
+        <v>460</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>461</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>462</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>463</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="33" t="s">
+        <v>466</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>467</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>462</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>468</v>
+      </c>
+      <c r="F11" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="32" t="s">
+        <v>470</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>471</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>462</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>472</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="33" t="s">
+        <v>474</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>475</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>462</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>476</v>
+      </c>
+      <c r="F13" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="32" t="s">
+        <v>478</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>479</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>462</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>480</v>
+      </c>
+      <c r="F14" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="33" t="s">
+        <v>482</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>483</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>484</v>
+      </c>
+      <c r="E15" s="24" t="s">
+        <v>485</v>
+      </c>
+      <c r="F15" s="33" t="s">
+        <v>486</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="32" t="s">
+        <v>488</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>489</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>462</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>490</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="33" t="s">
+        <v>492</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>493</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>462</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>494</v>
+      </c>
+      <c r="F17" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="32" t="s">
+        <v>496</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>497</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>462</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>498</v>
+      </c>
+      <c r="F18" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="33" t="s">
+        <v>500</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>501</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>462</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>502</v>
+      </c>
+      <c r="F19" s="33" t="s">
+        <v>503</v>
+      </c>
+      <c r="G19" s="24" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="32" t="s">
+        <v>505</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>506</v>
+      </c>
+      <c r="D20" s="32" t="s">
+        <v>462</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>507</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="33" t="s">
+        <v>509</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>510</v>
+      </c>
+      <c r="D21" s="33" t="s">
+        <v>462</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>511</v>
+      </c>
+      <c r="F21" s="33" t="s">
+        <v>503</v>
+      </c>
+      <c r="G21" s="24" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="32" t="s">
+        <v>513</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>514</v>
+      </c>
+      <c r="D22" s="32" t="s">
+        <v>462</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>515</v>
+      </c>
+      <c r="F22" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="33" t="s">
+        <v>517</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>518</v>
+      </c>
+      <c r="D23" s="33" t="s">
+        <v>462</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>519</v>
+      </c>
+      <c r="F23" s="33" t="s">
+        <v>520</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="32" t="s">
+        <v>522</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>523</v>
+      </c>
+      <c r="D24" s="32" t="s">
+        <v>462</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>524</v>
+      </c>
+      <c r="F24" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>527</v>
+      </c>
+      <c r="D25" s="33" t="s">
+        <v>462</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>528</v>
+      </c>
+      <c r="F25" s="33" t="s">
+        <v>486</v>
+      </c>
+      <c r="G25" s="24" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="32" t="s">
+        <v>530</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>531</v>
+      </c>
+      <c r="D26" s="32" t="s">
+        <v>462</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>532</v>
+      </c>
+      <c r="F26" s="32" t="s">
+        <v>486</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>535</v>
+      </c>
+      <c r="D27" s="33" t="s">
+        <v>462</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>536</v>
+      </c>
+      <c r="F27" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="G27" s="24" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="32" t="s">
+        <v>538</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>539</v>
+      </c>
+      <c r="D28" s="32" t="s">
+        <v>484</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="F28" s="32" t="s">
+        <v>486</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="33" t="s">
+        <v>541</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>542</v>
+      </c>
+      <c r="D29" s="33" t="s">
+        <v>462</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>524</v>
+      </c>
+      <c r="F29" s="33" t="s">
+        <v>503</v>
+      </c>
+      <c r="G29" s="24" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="32" t="s">
+        <v>544</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>545</v>
+      </c>
+      <c r="D30" s="32" t="s">
+        <v>484</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>546</v>
+      </c>
+      <c r="F30" s="32" t="s">
+        <v>486</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="33" t="s">
+        <v>548</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>549</v>
+      </c>
+      <c r="D31" s="33" t="s">
+        <v>484</v>
+      </c>
+      <c r="E31" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="F31" s="33" t="s">
+        <v>503</v>
+      </c>
+      <c r="G31" s="24" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="5" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="19" t="s">
+        <v>360</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>552</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>553</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>554</v>
+      </c>
+      <c r="H34" s="19" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="32" t="s">
+        <v>367</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="D35" s="32" t="s">
+        <v>492</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>555</v>
+      </c>
+      <c r="F35" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G35" s="20"/>
+      <c r="H35" s="21" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="33" t="s">
+        <v>367</v>
+      </c>
+      <c r="C36" s="24" t="s">
+        <v>370</v>
+      </c>
+      <c r="D36" s="33" t="s">
+        <v>492</v>
+      </c>
+      <c r="E36" s="24" t="s">
+        <v>556</v>
+      </c>
+      <c r="F36" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="G36" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="H36" s="25" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="32" t="s">
+        <v>367</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>372</v>
+      </c>
+      <c r="D37" s="32" t="s">
+        <v>460</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>558</v>
+      </c>
+      <c r="F37" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G37" s="20"/>
+      <c r="H37" s="21" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="33" t="s">
+        <v>367</v>
+      </c>
+      <c r="C38" s="24" t="s">
+        <v>374</v>
+      </c>
+      <c r="D38" s="33" t="s">
+        <v>460</v>
+      </c>
+      <c r="E38" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="F38" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="G38" s="24"/>
+      <c r="H38" s="25" t="n">
+        <v>37.4</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="32" t="s">
+        <v>367</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>375</v>
+      </c>
+      <c r="D39" s="32" t="s">
+        <v>460</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>558</v>
+      </c>
+      <c r="F39" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G39" s="20"/>
+      <c r="H39" s="21" t="n">
+        <v>61.6</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="33" t="s">
+        <v>367</v>
+      </c>
+      <c r="C40" s="24" t="s">
+        <v>376</v>
+      </c>
+      <c r="D40" s="33" t="s">
+        <v>460</v>
+      </c>
+      <c r="E40" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="F40" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="G40" s="24"/>
+      <c r="H40" s="25" t="n">
+        <v>49.3</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="32" t="s">
+        <v>377</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>378</v>
+      </c>
+      <c r="D41" s="32" t="s">
+        <v>559</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>560</v>
+      </c>
+      <c r="F41" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G41" s="20"/>
+      <c r="H41" s="21" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="33" t="s">
+        <v>377</v>
+      </c>
+      <c r="C42" s="24" t="s">
+        <v>380</v>
+      </c>
+      <c r="D42" s="33" t="s">
+        <v>488</v>
+      </c>
+      <c r="E42" s="24" t="s">
+        <v>561</v>
+      </c>
+      <c r="F42" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="G42" s="24"/>
+      <c r="H42" s="25" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="32" t="s">
+        <v>377</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>381</v>
+      </c>
+      <c r="D43" s="32" t="s">
+        <v>562</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>560</v>
+      </c>
+      <c r="F43" s="32" t="s">
+        <v>503</v>
+      </c>
+      <c r="G43" s="20" t="s">
+        <v>563</v>
+      </c>
+      <c r="H43" s="21" t="n">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="33" t="s">
+        <v>377</v>
+      </c>
+      <c r="C44" s="24" t="s">
+        <v>382</v>
+      </c>
+      <c r="D44" s="33" t="s">
+        <v>564</v>
+      </c>
+      <c r="E44" s="24" t="s">
+        <v>565</v>
+      </c>
+      <c r="F44" s="33" t="s">
+        <v>503</v>
+      </c>
+      <c r="G44" s="24" t="s">
+        <v>566</v>
+      </c>
+      <c r="H44" s="25" t="n">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="32" t="s">
+        <v>383</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>384</v>
+      </c>
+      <c r="D45" s="32" t="s">
+        <v>513</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="F45" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G45" s="20" t="s">
+        <v>568</v>
+      </c>
+      <c r="H45" s="21" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="33" t="s">
+        <v>383</v>
+      </c>
+      <c r="C46" s="24" t="s">
+        <v>386</v>
+      </c>
+      <c r="D46" s="33" t="s">
+        <v>513</v>
+      </c>
+      <c r="E46" s="24" t="s">
+        <v>569</v>
+      </c>
+      <c r="F46" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="G46" s="24"/>
+      <c r="H46" s="25" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="32" t="s">
+        <v>387</v>
+      </c>
+      <c r="C47" s="20" t="s">
+        <v>388</v>
+      </c>
+      <c r="D47" s="32" t="s">
+        <v>570</v>
+      </c>
+      <c r="E47" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="F47" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G47" s="20"/>
+      <c r="H47" s="21" t="n">
+        <v>61.7</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="33" t="s">
+        <v>387</v>
+      </c>
+      <c r="C48" s="24" t="s">
+        <v>390</v>
+      </c>
+      <c r="D48" s="33" t="s">
+        <v>570</v>
+      </c>
+      <c r="E48" s="24" t="s">
+        <v>571</v>
+      </c>
+      <c r="F48" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="G48" s="24"/>
+      <c r="H48" s="25" t="n">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="32" t="s">
+        <v>387</v>
+      </c>
+      <c r="C49" s="20" t="s">
+        <v>391</v>
+      </c>
+      <c r="D49" s="32" t="s">
+        <v>460</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>572</v>
+      </c>
+      <c r="F49" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G49" s="20"/>
+      <c r="H49" s="21" t="n">
+        <v>104.6</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="33" t="s">
+        <v>387</v>
+      </c>
+      <c r="C50" s="24" t="s">
+        <v>393</v>
+      </c>
+      <c r="D50" s="33" t="s">
+        <v>460</v>
+      </c>
+      <c r="E50" s="24" t="s">
+        <v>572</v>
+      </c>
+      <c r="F50" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="G50" s="24"/>
+      <c r="H50" s="25" t="n">
+        <v>1611.7</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="32" t="s">
+        <v>394</v>
+      </c>
+      <c r="C51" s="20" t="s">
+        <v>395</v>
+      </c>
+      <c r="D51" s="32" t="s">
+        <v>530</v>
+      </c>
+      <c r="E51" s="20" t="s">
+        <v>573</v>
+      </c>
+      <c r="F51" s="32" t="s">
+        <v>486</v>
+      </c>
+      <c r="G51" s="20" t="s">
+        <v>574</v>
+      </c>
+      <c r="H51" s="21" t="n">
+        <v>36.4</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="33" t="s">
+        <v>394</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>397</v>
+      </c>
+      <c r="D52" s="33" t="s">
+        <v>575</v>
+      </c>
+      <c r="E52" s="24" t="s">
+        <v>576</v>
+      </c>
+      <c r="F52" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="G52" s="24" t="s">
+        <v>577</v>
+      </c>
+      <c r="H52" s="25" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="32" t="s">
+        <v>394</v>
+      </c>
+      <c r="C53" s="20" t="s">
+        <v>398</v>
+      </c>
+      <c r="D53" s="32" t="s">
+        <v>575</v>
+      </c>
+      <c r="E53" s="20" t="s">
+        <v>576</v>
+      </c>
+      <c r="F53" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G53" s="20"/>
+      <c r="H53" s="21" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="33" t="s">
+        <v>394</v>
+      </c>
+      <c r="C54" s="24" t="s">
+        <v>399</v>
+      </c>
+      <c r="D54" s="33" t="s">
+        <v>578</v>
+      </c>
+      <c r="E54" s="24" t="s">
+        <v>579</v>
+      </c>
+      <c r="F54" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="G54" s="24"/>
+      <c r="H54" s="25" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="32" t="s">
+        <v>394</v>
+      </c>
+      <c r="C55" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="D55" s="32" t="s">
+        <v>522</v>
+      </c>
+      <c r="E55" s="20" t="s">
+        <v>580</v>
+      </c>
+      <c r="F55" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G55" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="H55" s="21" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="33" t="s">
+        <v>394</v>
+      </c>
+      <c r="C56" s="24" t="s">
+        <v>401</v>
+      </c>
+      <c r="D56" s="33" t="s">
+        <v>530</v>
+      </c>
+      <c r="E56" s="24" t="s">
+        <v>582</v>
+      </c>
+      <c r="F56" s="33" t="s">
+        <v>486</v>
+      </c>
+      <c r="G56" s="24" t="s">
+        <v>583</v>
+      </c>
+      <c r="H56" s="25" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="32" t="s">
+        <v>394</v>
+      </c>
+      <c r="C57" s="20" t="s">
+        <v>403</v>
+      </c>
+      <c r="D57" s="32" t="s">
+        <v>492</v>
+      </c>
+      <c r="E57" s="20" t="s">
+        <v>582</v>
+      </c>
+      <c r="F57" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G57" s="20"/>
+      <c r="H57" s="21" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="33" t="s">
+        <v>394</v>
+      </c>
+      <c r="C58" s="24" t="s">
+        <v>404</v>
+      </c>
+      <c r="D58" s="33" t="s">
+        <v>522</v>
+      </c>
+      <c r="E58" s="24" t="s">
+        <v>582</v>
+      </c>
+      <c r="F58" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="G58" s="24"/>
+      <c r="H58" s="25" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="32" t="s">
+        <v>367</v>
+      </c>
+      <c r="C59" s="20" t="s">
+        <v>405</v>
+      </c>
+      <c r="D59" s="32" t="s">
+        <v>505</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>584</v>
+      </c>
+      <c r="F59" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G59" s="20"/>
+      <c r="H59" s="21" t="n">
+        <v>65.4</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="33" t="s">
+        <v>367</v>
+      </c>
+      <c r="C60" s="24" t="s">
+        <v>407</v>
+      </c>
+      <c r="D60" s="33" t="s">
+        <v>505</v>
+      </c>
+      <c r="E60" s="24" t="s">
+        <v>584</v>
+      </c>
+      <c r="F60" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="G60" s="24"/>
+      <c r="H60" s="25" t="n">
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="32" t="s">
+        <v>367</v>
+      </c>
+      <c r="C61" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="D61" s="32" t="s">
+        <v>505</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>585</v>
+      </c>
+      <c r="F61" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G61" s="20" t="s">
+        <v>586</v>
+      </c>
+      <c r="H61" s="21" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="33" t="s">
+        <v>410</v>
+      </c>
+      <c r="C62" s="24" t="s">
+        <v>411</v>
+      </c>
+      <c r="D62" s="33" t="s">
+        <v>492</v>
+      </c>
+      <c r="E62" s="24" t="s">
+        <v>587</v>
+      </c>
+      <c r="F62" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="G62" s="24" t="s">
+        <v>588</v>
+      </c>
+      <c r="H62" s="25" t="n">
+        <v>90.9</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="32" t="s">
+        <v>410</v>
+      </c>
+      <c r="C63" s="20" t="s">
+        <v>413</v>
+      </c>
+      <c r="D63" s="32" t="s">
+        <v>492</v>
+      </c>
+      <c r="E63" s="20" t="s">
+        <v>587</v>
+      </c>
+      <c r="F63" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G63" s="20"/>
+      <c r="H63" s="21" t="n">
+        <v>66.2</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="33" t="s">
+        <v>410</v>
+      </c>
+      <c r="C64" s="24" t="s">
+        <v>415</v>
+      </c>
+      <c r="D64" s="33" t="s">
+        <v>460</v>
+      </c>
+      <c r="E64" s="24" t="s">
+        <v>589</v>
+      </c>
+      <c r="F64" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="G64" s="24"/>
+      <c r="H64" s="25" t="n">
+        <v>62.3</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B65" s="32" t="s">
+        <v>416</v>
+      </c>
+      <c r="C65" s="20" t="s">
+        <v>417</v>
+      </c>
+      <c r="D65" s="32" t="s">
+        <v>590</v>
+      </c>
+      <c r="E65" s="20" t="s">
+        <v>591</v>
+      </c>
+      <c r="F65" s="32" t="s">
+        <v>503</v>
+      </c>
+      <c r="G65" s="20" t="s">
+        <v>592</v>
+      </c>
+      <c r="H65" s="21" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="33" t="s">
+        <v>416</v>
+      </c>
+      <c r="C66" s="24" t="s">
+        <v>419</v>
+      </c>
+      <c r="D66" s="33" t="s">
+        <v>593</v>
+      </c>
+      <c r="E66" s="24" t="s">
+        <v>594</v>
+      </c>
+      <c r="F66" s="33" t="s">
+        <v>503</v>
+      </c>
+      <c r="G66" s="24" t="s">
+        <v>595</v>
+      </c>
+      <c r="H66" s="25" t="n">
+        <v>8.2</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="32" t="s">
+        <v>416</v>
+      </c>
+      <c r="C67" s="20" t="s">
+        <v>421</v>
+      </c>
+      <c r="D67" s="32" t="s">
+        <v>593</v>
+      </c>
+      <c r="E67" s="20" t="s">
+        <v>594</v>
+      </c>
+      <c r="F67" s="32" t="s">
+        <v>503</v>
+      </c>
+      <c r="G67" s="20" t="s">
+        <v>596</v>
+      </c>
+      <c r="H67" s="21" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="33" t="s">
+        <v>416</v>
+      </c>
+      <c r="C68" s="24" t="s">
+        <v>423</v>
+      </c>
+      <c r="D68" s="33" t="s">
+        <v>593</v>
+      </c>
+      <c r="E68" s="24" t="s">
+        <v>594</v>
+      </c>
+      <c r="F68" s="33" t="s">
+        <v>503</v>
+      </c>
+      <c r="G68" s="24" t="s">
+        <v>596</v>
+      </c>
+      <c r="H68" s="25" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="32" t="s">
+        <v>416</v>
+      </c>
+      <c r="C69" s="20" t="s">
+        <v>425</v>
+      </c>
+      <c r="D69" s="32" t="s">
+        <v>593</v>
+      </c>
+      <c r="E69" s="20" t="s">
+        <v>594</v>
+      </c>
+      <c r="F69" s="32" t="s">
+        <v>503</v>
+      </c>
+      <c r="G69" s="20" t="s">
+        <v>596</v>
+      </c>
+      <c r="H69" s="21" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="33" t="s">
+        <v>416</v>
+      </c>
+      <c r="C70" s="24" t="s">
+        <v>427</v>
+      </c>
+      <c r="D70" s="33" t="s">
+        <v>593</v>
+      </c>
+      <c r="E70" s="24" t="s">
+        <v>594</v>
+      </c>
+      <c r="F70" s="33" t="s">
+        <v>503</v>
+      </c>
+      <c r="G70" s="24" t="s">
+        <v>597</v>
+      </c>
+      <c r="H70" s="25" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="32" t="s">
+        <v>429</v>
+      </c>
+      <c r="C71" s="20" t="s">
+        <v>430</v>
+      </c>
+      <c r="D71" s="32" t="s">
+        <v>598</v>
+      </c>
+      <c r="E71" s="20" t="s">
+        <v>599</v>
+      </c>
+      <c r="F71" s="32" t="s">
+        <v>503</v>
+      </c>
+      <c r="G71" s="20" t="s">
+        <v>600</v>
+      </c>
+      <c r="H71" s="21" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B72" s="33" t="s">
+        <v>429</v>
+      </c>
+      <c r="C72" s="24" t="s">
+        <v>432</v>
+      </c>
+      <c r="D72" s="33" t="s">
+        <v>598</v>
+      </c>
+      <c r="E72" s="24" t="s">
+        <v>599</v>
+      </c>
+      <c r="F72" s="33" t="s">
+        <v>503</v>
+      </c>
+      <c r="G72" s="24" t="s">
+        <v>596</v>
+      </c>
+      <c r="H72" s="25" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B73" s="32" t="s">
+        <v>433</v>
+      </c>
+      <c r="C73" s="20" t="s">
+        <v>434</v>
+      </c>
+      <c r="D73" s="32" t="s">
+        <v>601</v>
+      </c>
+      <c r="E73" s="20" t="s">
+        <v>602</v>
+      </c>
+      <c r="F73" s="32" t="s">
+        <v>503</v>
+      </c>
+      <c r="G73" s="20" t="s">
+        <v>596</v>
+      </c>
+      <c r="H73" s="21" t="n">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B74" s="33" t="s">
+        <v>433</v>
+      </c>
+      <c r="C74" s="24" t="s">
+        <v>436</v>
+      </c>
+      <c r="D74" s="33" t="s">
+        <v>601</v>
+      </c>
+      <c r="E74" s="24" t="s">
+        <v>602</v>
+      </c>
+      <c r="F74" s="33" t="s">
+        <v>503</v>
+      </c>
+      <c r="G74" s="24" t="s">
+        <v>596</v>
+      </c>
+      <c r="H74" s="25" t="n">
+        <v>3.05</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="32" t="s">
+        <v>394</v>
+      </c>
+      <c r="C75" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="D75" s="32" t="s">
+        <v>522</v>
+      </c>
+      <c r="E75" s="20" t="s">
+        <v>603</v>
+      </c>
+      <c r="F75" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G75" s="20" t="s">
+        <v>604</v>
+      </c>
+      <c r="H75" s="21" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="33" t="s">
+        <v>383</v>
+      </c>
+      <c r="C76" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="D76" s="33" t="s">
+        <v>605</v>
+      </c>
+      <c r="E76" s="24" t="s">
+        <v>606</v>
+      </c>
+      <c r="F76" s="33" t="s">
+        <v>486</v>
+      </c>
+      <c r="G76" s="24" t="s">
+        <v>607</v>
+      </c>
+      <c r="H76" s="25" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="32" t="s">
+        <v>383</v>
+      </c>
+      <c r="C77" s="20" t="s">
+        <v>441</v>
+      </c>
+      <c r="D77" s="32" t="s">
+        <v>478</v>
+      </c>
+      <c r="E77" s="20" t="s">
+        <v>608</v>
+      </c>
+      <c r="F77" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G77" s="20"/>
+      <c r="H77" s="21" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="33" t="s">
+        <v>383</v>
+      </c>
+      <c r="C78" s="24" t="s">
+        <v>443</v>
+      </c>
+      <c r="D78" s="33" t="s">
+        <v>548</v>
+      </c>
+      <c r="E78" s="24" t="s">
+        <v>609</v>
+      </c>
+      <c r="F78" s="33" t="s">
+        <v>503</v>
+      </c>
+      <c r="G78" s="24" t="s">
+        <v>610</v>
+      </c>
+      <c r="H78" s="25" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B79" s="32" t="s">
+        <v>383</v>
+      </c>
+      <c r="C79" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="D79" s="32" t="s">
+        <v>611</v>
+      </c>
+      <c r="E79" s="20" t="s">
+        <v>609</v>
+      </c>
+      <c r="F79" s="32" t="s">
+        <v>503</v>
+      </c>
+      <c r="G79" s="20" t="s">
+        <v>612</v>
+      </c>
+      <c r="H79" s="21" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="33" t="s">
+        <v>383</v>
+      </c>
+      <c r="C80" s="24" t="s">
+        <v>446</v>
+      </c>
+      <c r="D80" s="33" t="s">
+        <v>613</v>
+      </c>
+      <c r="E80" s="24" t="s">
+        <v>614</v>
+      </c>
+      <c r="F80" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="G80" s="24" t="s">
+        <v>615</v>
+      </c>
+      <c r="H80" s="25" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B81" s="32" t="s">
+        <v>367</v>
+      </c>
+      <c r="C81" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="D81" s="32" t="s">
+        <v>505</v>
+      </c>
+      <c r="E81" s="20" t="s">
+        <v>616</v>
+      </c>
+      <c r="F81" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G81" s="20"/>
+      <c r="H81" s="21" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B83" s="5" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B84" s="19" t="s">
+        <v>618</v>
+      </c>
+      <c r="C84" s="19" t="s">
+        <v>330</v>
+      </c>
+      <c r="D84" s="19" t="s">
+        <v>619</v>
+      </c>
+      <c r="E84" s="19" t="s">
+        <v>620</v>
+      </c>
+      <c r="F84" s="19" t="s">
+        <v>621</v>
+      </c>
+      <c r="G84" s="19" t="s">
+        <v>622</v>
+      </c>
+      <c r="H84" s="19" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B85" s="32" t="s">
+        <v>623</v>
+      </c>
+      <c r="C85" s="20" t="s">
+        <v>624</v>
+      </c>
+      <c r="D85" s="32" t="s">
+        <v>625</v>
+      </c>
+      <c r="E85" s="20" t="s">
+        <v>626</v>
+      </c>
+      <c r="F85" s="20" t="s">
+        <v>627</v>
+      </c>
+      <c r="G85" s="20" t="s">
+        <v>628</v>
+      </c>
+      <c r="H85" s="32" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="33" t="s">
+        <v>630</v>
+      </c>
+      <c r="C86" s="24" t="s">
+        <v>631</v>
+      </c>
+      <c r="D86" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="E86" s="24" t="s">
+        <v>626</v>
+      </c>
+      <c r="F86" s="24" t="s">
+        <v>632</v>
+      </c>
+      <c r="G86" s="24" t="s">
+        <v>633</v>
+      </c>
+      <c r="H86" s="33" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="32" t="s">
+        <v>634</v>
+      </c>
+      <c r="C87" s="20" t="s">
+        <v>635</v>
+      </c>
+      <c r="D87" s="32" t="s">
+        <v>625</v>
+      </c>
+      <c r="E87" s="20" t="s">
+        <v>626</v>
+      </c>
+      <c r="F87" s="20" t="s">
+        <v>636</v>
+      </c>
+      <c r="G87" s="20" t="s">
+        <v>637</v>
+      </c>
+      <c r="H87" s="32" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B88" s="33" t="s">
+        <v>638</v>
+      </c>
+      <c r="C88" s="24" t="s">
+        <v>639</v>
+      </c>
+      <c r="D88" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="E88" s="24" t="s">
+        <v>640</v>
+      </c>
+      <c r="F88" s="24" t="s">
+        <v>641</v>
+      </c>
+      <c r="G88" s="24" t="s">
+        <v>642</v>
+      </c>
+      <c r="H88" s="33" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B89" s="32" t="s">
+        <v>643</v>
+      </c>
+      <c r="C89" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="D89" s="32" t="s">
+        <v>625</v>
+      </c>
+      <c r="E89" s="20" t="s">
+        <v>645</v>
+      </c>
+      <c r="F89" s="20" t="s">
+        <v>646</v>
+      </c>
+      <c r="G89" s="20" t="s">
+        <v>647</v>
+      </c>
+      <c r="H89" s="32" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B90" s="33" t="s">
+        <v>648</v>
+      </c>
+      <c r="C90" s="24" t="s">
+        <v>649</v>
+      </c>
+      <c r="D90" s="33" t="s">
+        <v>650</v>
+      </c>
+      <c r="E90" s="24" t="s">
+        <v>651</v>
+      </c>
+      <c r="F90" s="24" t="s">
+        <v>652</v>
+      </c>
+      <c r="G90" s="24" t="s">
+        <v>653</v>
+      </c>
+      <c r="H90" s="33" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B91" s="32" t="s">
+        <v>655</v>
+      </c>
+      <c r="C91" s="20" t="s">
+        <v>656</v>
+      </c>
+      <c r="D91" s="32" t="s">
+        <v>650</v>
+      </c>
+      <c r="E91" s="20" t="s">
+        <v>651</v>
+      </c>
+      <c r="F91" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="G91" s="20" t="s">
+        <v>657</v>
+      </c>
+      <c r="H91" s="32" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B92" s="33" t="s">
+        <v>658</v>
+      </c>
+      <c r="C92" s="24" t="s">
+        <v>659</v>
+      </c>
+      <c r="D92" s="33" t="s">
+        <v>650</v>
+      </c>
+      <c r="E92" s="24" t="s">
+        <v>651</v>
+      </c>
+      <c r="F92" s="24" t="s">
+        <v>652</v>
+      </c>
+      <c r="G92" s="24" t="s">
+        <v>660</v>
+      </c>
+      <c r="H92" s="33" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B93" s="32" t="s">
+        <v>661</v>
+      </c>
+      <c r="C93" s="20" t="s">
+        <v>662</v>
+      </c>
+      <c r="D93" s="32" t="s">
+        <v>650</v>
+      </c>
+      <c r="E93" s="20" t="s">
+        <v>626</v>
+      </c>
+      <c r="F93" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="G93" s="20" t="s">
+        <v>663</v>
+      </c>
+      <c r="H93" s="32" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B94" s="33" t="s">
+        <v>664</v>
+      </c>
+      <c r="C94" s="24" t="s">
+        <v>665</v>
+      </c>
+      <c r="D94" s="33" t="s">
+        <v>666</v>
+      </c>
+      <c r="E94" s="24" t="s">
+        <v>667</v>
+      </c>
+      <c r="F94" s="24" t="s">
+        <v>652</v>
+      </c>
+      <c r="G94" s="24" t="s">
+        <v>668</v>
+      </c>
+      <c r="H94" s="33" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B95" s="32" t="s">
+        <v>669</v>
+      </c>
+      <c r="C95" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="D95" s="32" t="s">
+        <v>666</v>
+      </c>
+      <c r="E95" s="20" t="s">
+        <v>667</v>
+      </c>
+      <c r="F95" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="G95" s="20" t="s">
+        <v>671</v>
+      </c>
+      <c r="H95" s="32" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B96" s="33" t="s">
+        <v>672</v>
+      </c>
+      <c r="C96" s="24" t="s">
+        <v>673</v>
+      </c>
+      <c r="D96" s="33" t="s">
+        <v>674</v>
+      </c>
+      <c r="E96" s="24" t="s">
+        <v>667</v>
+      </c>
+      <c r="F96" s="24" t="s">
+        <v>652</v>
+      </c>
+      <c r="G96" s="24" t="s">
+        <v>675</v>
+      </c>
+      <c r="H96" s="33" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B97" s="32" t="s">
+        <v>676</v>
+      </c>
+      <c r="C97" s="20" t="s">
+        <v>677</v>
+      </c>
+      <c r="D97" s="32" t="s">
+        <v>650</v>
+      </c>
+      <c r="E97" s="20" t="s">
+        <v>626</v>
+      </c>
+      <c r="F97" s="20" t="s">
+        <v>678</v>
+      </c>
+      <c r="G97" s="20" t="s">
+        <v>679</v>
+      </c>
+      <c r="H97" s="32" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B98" s="33" t="s">
+        <v>681</v>
+      </c>
+      <c r="C98" s="24" t="s">
+        <v>682</v>
+      </c>
+      <c r="D98" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="E98" s="24" t="s">
+        <v>640</v>
+      </c>
+      <c r="F98" s="24" t="s">
+        <v>652</v>
+      </c>
+      <c r="G98" s="24" t="s">
+        <v>683</v>
+      </c>
+      <c r="H98" s="33" t="s">
+        <v>654</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B7:H7"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FFB7B5AC"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B1:D15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -6049,124 +8887,124 @@
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="17" t="s">
-        <v>438</v>
+        <v>684</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="19" t="s">
-        <v>439</v>
+        <v>685</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>440</v>
+        <v>686</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>441</v>
+        <v>687</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="20" t="s">
-        <v>442</v>
+        <v>688</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>443</v>
+        <v>689</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>444</v>
+        <v>690</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="24" t="s">
-        <v>445</v>
+        <v>691</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>446</v>
+        <v>692</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>447</v>
+        <v>693</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="20" t="s">
-        <v>448</v>
+        <v>694</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>449</v>
+        <v>695</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>447</v>
+        <v>693</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="24" t="s">
-        <v>450</v>
+        <v>696</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>451</v>
+        <v>697</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>447</v>
+        <v>693</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="20" t="s">
-        <v>452</v>
+        <v>698</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>453</v>
+        <v>699</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>454</v>
+        <v>700</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="24" t="s">
-        <v>455</v>
+        <v>701</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>456</v>
+        <v>702</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>457</v>
+        <v>703</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="20" t="s">
-        <v>458</v>
+        <v>704</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>459</v>
+        <v>705</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>460</v>
+        <v>706</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="24" t="s">
-        <v>461</v>
+        <v>707</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>462</v>
+        <v>708</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>463</v>
+        <v>709</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="20" t="s">
-        <v>464</v>
+        <v>710</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>465</v>
+        <v>711</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>466</v>
+        <v>712</v>
       </c>
     </row>
   </sheetData>
@@ -6183,7 +9021,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FFB7B5AC"/>
@@ -6202,12 +9040,12 @@
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>467</v>
+        <v>713</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="17" t="s">
-        <v>468</v>
+        <v>714</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
@@ -6215,298 +9053,114 @@
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="19" t="s">
-        <v>469</v>
+        <v>715</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>470</v>
+        <v>716</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="20" t="s">
-        <v>472</v>
+        <v>717</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>473</v>
+        <v>718</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>474</v>
+        <v>719</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>475</v>
+        <v>720</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="24" t="s">
-        <v>476</v>
+        <v>721</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>477</v>
+        <v>722</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>474</v>
+        <v>719</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>475</v>
+        <v>720</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="20" t="s">
-        <v>478</v>
+        <v>723</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>479</v>
+        <v>724</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>474</v>
+        <v>719</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>475</v>
+        <v>720</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="24" t="s">
-        <v>480</v>
+        <v>725</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>481</v>
+        <v>726</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>482</v>
+        <v>727</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>483</v>
+        <v>728</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="20" t="s">
-        <v>484</v>
+        <v>729</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>485</v>
+        <v>730</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>486</v>
+        <v>731</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>487</v>
+        <v>732</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="24" t="s">
-        <v>488</v>
+        <v>733</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>489</v>
+        <v>734</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>474</v>
+        <v>719</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>490</v>
+        <v>735</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="20" t="s">
-        <v>491</v>
+        <v>736</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>492</v>
+        <v>737</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>474</v>
+        <v>719</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>493</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B3:E3"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <tabColor rgb="FFB7B5AC"/>
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="B1:E15"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="1.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="44"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="17" t="s">
-        <v>494</v>
-      </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-    </row>
-    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="19" t="s">
-        <v>495</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>496</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>328</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="32" t="s">
-        <v>497</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>498</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>499</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="33" t="s">
-        <v>501</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>502</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>503</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="32" t="s">
-        <v>505</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>502</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>506</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="33" t="s">
-        <v>508</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>502</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>509</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="32" t="s">
-        <v>511</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>512</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>513</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="33" t="s">
-        <v>514</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>512</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>515</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="32" t="s">
-        <v>517</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>518</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>519</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="33" t="s">
-        <v>521</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>522</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>523</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="32" t="s">
-        <v>525</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>502</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>526</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>527</v>
+        <v>738</v>
       </c>
     </row>
   </sheetData>
@@ -6529,6 +9183,190 @@
     <tabColor rgb="FFB7B5AC"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B1:E15"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="1.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="44"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="17" t="s">
+        <v>739</v>
+      </c>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+    </row>
+    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="19" t="s">
+        <v>618</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>619</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>330</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="32" t="s">
+        <v>740</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>741</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>742</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="33" t="s">
+        <v>744</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>625</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>745</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="32" t="s">
+        <v>747</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>625</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>748</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="33" t="s">
+        <v>750</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>625</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>751</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="32" t="s">
+        <v>753</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>650</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>754</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="33" t="s">
+        <v>755</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>650</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>756</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="32" t="s">
+        <v>758</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>666</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>759</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="33" t="s">
+        <v>761</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>674</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>762</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="32" t="s">
+        <v>763</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>625</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>764</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>765</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:E3"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FFB7B5AC"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B1:D27"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -6541,256 +9379,256 @@
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>528</v>
+        <v>766</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="17" t="s">
-        <v>529</v>
+        <v>767</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="19" t="s">
-        <v>530</v>
+        <v>768</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>531</v>
+        <v>769</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>532</v>
+        <v>770</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="20" t="s">
-        <v>533</v>
+        <v>771</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>534</v>
+        <v>772</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>535</v>
+        <v>773</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="24" t="s">
-        <v>536</v>
+        <v>774</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>537</v>
+        <v>775</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>538</v>
+        <v>776</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="20" t="s">
-        <v>539</v>
+        <v>777</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>540</v>
+        <v>778</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>541</v>
+        <v>779</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="24" t="s">
-        <v>460</v>
+        <v>706</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>542</v>
+        <v>780</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>543</v>
+        <v>781</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="20" t="s">
-        <v>544</v>
+        <v>782</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>545</v>
+        <v>783</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>546</v>
+        <v>784</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="24" t="s">
-        <v>547</v>
+        <v>785</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>548</v>
+        <v>786</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>549</v>
+        <v>787</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="20" t="s">
-        <v>550</v>
+        <v>788</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>551</v>
+        <v>789</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>552</v>
+        <v>790</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="24" t="s">
-        <v>553</v>
+        <v>791</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>554</v>
+        <v>792</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>555</v>
+        <v>793</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="20" t="s">
-        <v>556</v>
+        <v>794</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>557</v>
+        <v>795</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>558</v>
+        <v>796</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="24" t="s">
-        <v>559</v>
+        <v>797</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>560</v>
+        <v>798</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>561</v>
+        <v>799</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="20" t="s">
-        <v>562</v>
+        <v>800</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>563</v>
+        <v>801</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>564</v>
+        <v>802</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="24" t="s">
-        <v>565</v>
+        <v>803</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>566</v>
+        <v>804</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>567</v>
+        <v>805</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="20" t="s">
-        <v>568</v>
+        <v>806</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>569</v>
+        <v>807</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>570</v>
+        <v>808</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="24" t="s">
-        <v>571</v>
+        <v>809</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>572</v>
+        <v>810</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>573</v>
+        <v>811</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="20" t="s">
-        <v>574</v>
+        <v>812</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>575</v>
+        <v>813</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>576</v>
+        <v>814</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="24" t="s">
-        <v>577</v>
+        <v>815</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>578</v>
+        <v>816</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>579</v>
+        <v>817</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="20" t="s">
-        <v>580</v>
+        <v>818</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>581</v>
+        <v>819</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>582</v>
+        <v>820</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="24" t="s">
-        <v>583</v>
+        <v>821</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>542</v>
+        <v>780</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>584</v>
+        <v>822</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="20" t="s">
-        <v>585</v>
+        <v>823</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>586</v>
+        <v>824</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>587</v>
+        <v>825</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="24" t="s">
-        <v>588</v>
+        <v>826</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>589</v>
+        <v>827</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>590</v>
+        <v>828</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="20" t="s">
-        <v>591</v>
+        <v>829</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>592</v>
+        <v>830</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>593</v>
+        <v>831</v>
       </c>
     </row>
   </sheetData>
@@ -6828,12 +9666,12 @@
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
@@ -6847,12 +9685,12 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -6866,7 +9704,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -6880,39 +9718,39 @@
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="19" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J9" s="19" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="20" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C10" s="21" t="n">
         <v>1.4518</v>
@@ -6944,7 +9782,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C11" s="25" t="n">
         <v>1.638</v>
@@ -6976,7 +9814,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="20" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C12" s="21" t="n">
         <v>1.6363</v>
@@ -7008,7 +9846,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="24" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C13" s="25" t="n">
         <v>2.3078</v>
@@ -7040,7 +9878,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="20" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C14" s="21" t="n">
         <v>1.8729</v>
@@ -7072,7 +9910,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="24" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C15" s="25" t="n">
         <v>1.9606</v>
@@ -7104,7 +9942,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="20" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C16" s="21" t="n">
         <v>2.1117</v>
@@ -7136,7 +9974,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C17" s="25" t="n">
         <v>2.0993</v>
@@ -7168,7 +10006,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C18" s="21" t="n">
         <v>2.0516</v>
@@ -7200,7 +10038,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C19" s="25" t="n">
         <v>1.9018</v>
@@ -7232,7 +10070,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="20" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C20" s="21" t="n">
         <v>1.959</v>
@@ -7264,7 +10102,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="24" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C21" s="25" t="n">
         <v>2.0018</v>
@@ -7296,7 +10134,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="20" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C22" s="21" t="n">
         <v>1.9907</v>
@@ -7328,7 +10166,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="24" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C23" s="25" t="n">
         <v>2.1019</v>
@@ -7360,7 +10198,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="20" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C24" s="21" t="n">
         <v>1.839</v>
@@ -7392,7 +10230,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="24" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C25" s="25" t="n">
         <v>1.8341</v>
@@ -7424,7 +10262,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="20" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C26" s="21" t="n">
         <v>1.6959</v>
@@ -7456,7 +10294,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C27" s="25" t="n">
         <v>1.418</v>
@@ -7488,7 +10326,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="20" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C28" s="21" t="n">
         <v>1.7741</v>
@@ -7520,7 +10358,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C29" s="25" t="n">
         <v>1.5007</v>
@@ -7552,7 +10390,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="20" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C30" s="21" t="n">
         <v>1.4696</v>
@@ -7584,7 +10422,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C31" s="25" t="n">
         <v>1.1462</v>
@@ -7616,7 +10454,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="20" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C32" s="21" t="n">
         <v>1.7586</v>
@@ -7648,7 +10486,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="24" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C33" s="25" t="n">
         <v>1.31</v>
@@ -7680,7 +10518,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C34" s="21" t="n">
         <v>1.5351</v>
@@ -7712,7 +10550,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="24" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C35" s="25" t="n">
         <v>1.4267</v>
@@ -7744,7 +10582,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C36" s="29" t="n">
         <f aca="false">AVERAGE(C10:C35)</f>
@@ -7785,7 +10623,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="28" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C37" s="29" t="n">
         <f aca="false">SUMPRODUCT(C10:C35,$K$10:$K$35)/SUM($K$10:$K$35)</f>
@@ -7843,7 +10681,7 @@
     <tabColor rgb="FFB7B5AC"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:L36"/>
+  <dimension ref="B1:M36"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="1.2"/>
@@ -7853,17 +10691,18 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="17" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
@@ -7878,12 +10717,12 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -7898,7 +10737,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -7913,42 +10752,45 @@
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="19" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J9" s="19" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L9" s="19" t="s">
-        <v>111</v>
+        <v>113</v>
+      </c>
+      <c r="M9" s="19" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C10" s="21" t="n">
         <v>2.3078</v>
@@ -7978,12 +10820,15 @@
         <v>1.365</v>
       </c>
       <c r="L10" s="32" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="M10" s="23" t="n">
+        <v>3488.8</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="24" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C11" s="25" t="n">
         <v>2.1117</v>
@@ -8013,12 +10858,15 @@
         <v>0.1694</v>
       </c>
       <c r="L11" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>481</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C12" s="21" t="n">
         <v>2.1019</v>
@@ -8048,12 +10896,15 @@
         <v>0.0705</v>
       </c>
       <c r="L12" s="32" t="s">
-        <v>113</v>
+        <v>115</v>
+      </c>
+      <c r="M12" s="23" t="n">
+        <v>220.2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C13" s="25" t="n">
         <v>2.0993</v>
@@ -8083,12 +10934,15 @@
         <v>0.3758</v>
       </c>
       <c r="L13" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>1112.1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C14" s="21" t="n">
         <v>2.0516</v>
@@ -8118,12 +10972,15 @@
         <v>0.0943</v>
       </c>
       <c r="L14" s="32" t="s">
-        <v>113</v>
+        <v>115</v>
+      </c>
+      <c r="M14" s="23" t="n">
+        <v>276.5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="24" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C15" s="25" t="n">
         <v>2.0018</v>
@@ -8153,12 +11010,15 @@
         <v>0.2577</v>
       </c>
       <c r="L15" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>785.5</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="20" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C16" s="21" t="n">
         <v>1.9907</v>
@@ -8188,12 +11048,15 @@
         <v>0.1931</v>
       </c>
       <c r="L16" s="32" t="s">
-        <v>113</v>
+        <v>115</v>
+      </c>
+      <c r="M16" s="23" t="n">
+        <v>601.2</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="24" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C17" s="25" t="n">
         <v>1.9606</v>
@@ -8223,12 +11086,15 @@
         <v>0.8813</v>
       </c>
       <c r="L17" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>2835.3</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="20" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C18" s="21" t="n">
         <v>1.959</v>
@@ -8258,12 +11124,15 @@
         <v>3.4094</v>
       </c>
       <c r="L18" s="32" t="s">
-        <v>113</v>
+        <v>115</v>
+      </c>
+      <c r="M18" s="23" t="n">
+        <v>10677.8</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C19" s="25" t="n">
         <v>1.9018</v>
@@ -8293,12 +11162,15 @@
         <v>0.8479</v>
       </c>
       <c r="L19" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
+      </c>
+      <c r="M19" s="27" t="n">
+        <v>2679.2</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="20" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C20" s="21" t="n">
         <v>1.8729</v>
@@ -8328,12 +11200,15 @@
         <v>0.2089</v>
       </c>
       <c r="L20" s="32" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="M20" s="23" t="n">
+        <v>831.6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C21" s="25" t="n">
         <v>1.839</v>
@@ -8363,12 +11238,15 @@
         <v>0.1617</v>
       </c>
       <c r="L21" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>558.9</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="20" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C22" s="21" t="n">
         <v>1.8341</v>
@@ -8398,12 +11276,15 @@
         <v>0.5887</v>
       </c>
       <c r="L22" s="32" t="s">
-        <v>113</v>
+        <v>115</v>
+      </c>
+      <c r="M22" s="23" t="n">
+        <v>2093.9</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="24" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C23" s="25" t="n">
         <v>1.7741</v>
@@ -8433,12 +11314,15 @@
         <v>2.4164</v>
       </c>
       <c r="L23" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>8574.3</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="20" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C24" s="21" t="n">
         <v>1.7586</v>
@@ -8468,12 +11352,15 @@
         <v>0.5822</v>
       </c>
       <c r="L24" s="32" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="M24" s="23" t="n">
+        <v>2126.7</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C25" s="25" t="n">
         <v>1.6959</v>
@@ -8503,12 +11390,15 @@
         <v>1.6858</v>
       </c>
       <c r="L25" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>6925.6</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="20" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C26" s="21" t="n">
         <v>1.638</v>
@@ -8538,12 +11428,15 @@
         <v>0.4176</v>
       </c>
       <c r="L26" s="32" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="M26" s="23" t="n">
+        <v>1454.7</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C27" s="25" t="n">
         <v>1.6363</v>
@@ -8573,12 +11466,15 @@
         <v>4.4268</v>
       </c>
       <c r="L27" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="M27" s="27" t="n">
+        <v>16714.1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C28" s="21" t="n">
         <v>1.5351</v>
@@ -8608,12 +11504,15 @@
         <v>0.5984</v>
       </c>
       <c r="L28" s="32" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="M28" s="23" t="n">
+        <v>3257.4</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C29" s="25" t="n">
         <v>1.5007</v>
@@ -8643,12 +11542,15 @@
         <v>1.9611</v>
       </c>
       <c r="L29" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="M29" s="27" t="n">
+        <v>8188.5</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="20" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C30" s="21" t="n">
         <v>1.4696</v>
@@ -8678,12 +11580,15 @@
         <v>0.7323</v>
       </c>
       <c r="L30" s="32" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="M30" s="23" t="n">
+        <v>2972.4</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="24" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C31" s="25" t="n">
         <v>1.4518</v>
@@ -8713,12 +11618,15 @@
         <v>0.8728</v>
       </c>
       <c r="L31" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="M31" s="27" t="n">
+        <v>3910.6</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="20" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C32" s="21" t="n">
         <v>1.4267</v>
@@ -8748,12 +11656,15 @@
         <v>0.9654</v>
       </c>
       <c r="L32" s="32" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="M32" s="23" t="n">
+        <v>6381.3</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C33" s="25" t="n">
         <v>1.418</v>
@@ -8783,12 +11694,15 @@
         <v>2.0846</v>
       </c>
       <c r="L33" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="M33" s="27" t="n">
+        <v>10529.7</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="20" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C34" s="21" t="n">
         <v>1.31</v>
@@ -8818,12 +11732,15 @@
         <v>0.366</v>
       </c>
       <c r="L34" s="32" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="M34" s="23" t="n">
+        <v>3396.7</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C35" s="25" t="n">
         <v>1.1462</v>
@@ -8853,12 +11770,15 @@
         <v>0.267</v>
       </c>
       <c r="L35" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="M35" s="27" t="n">
+        <v>3547.6</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C36" s="29" t="n">
         <f aca="false">AVERAGE(C10:C35)</f>
@@ -8897,6 +11817,10 @@
         <v>1.00000384615385</v>
       </c>
       <c r="L36" s="34"/>
+      <c r="M36" s="31" t="n">
+        <f aca="false">SUM(M10:M35)</f>
+        <v>104621.6</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -8934,12 +11858,12 @@
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="17" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
@@ -8948,12 +11872,12 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -8962,7 +11886,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -8971,24 +11895,24 @@
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="19" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>34197.7</v>
@@ -9007,7 +11931,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C11" s="27" t="n">
         <v>30398</v>
@@ -9026,7 +11950,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="20" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>19675</v>
@@ -9045,7 +11969,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="24" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C13" s="27" t="n">
         <v>13724</v>
@@ -9064,7 +11988,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="20" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>7648.3</v>
@@ -9083,7 +12007,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="24" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C15" s="27" t="n">
         <v>-1021.3</v>
@@ -9102,7 +12026,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="28" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C16" s="31" t="n">
         <f aca="false">SUM(C10:C15)</f>
@@ -9123,7 +12047,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="28" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C17" s="31" t="n">
         <f aca="false">C10+C11</f>
@@ -9182,12 +12106,12 @@
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="17" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
@@ -9201,12 +12125,12 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -9220,7 +12144,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -9234,42 +12158,42 @@
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="19" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J9" s="19" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="34" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D10" s="30" t="n">
         <v>2.15</v>
@@ -9293,15 +12217,15 @@
         <v>0.385</v>
       </c>
       <c r="K10" s="28" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D11" s="26" t="n">
         <v>9.51</v>
@@ -9325,15 +12249,15 @@
         <v>0.465</v>
       </c>
       <c r="K11" s="24" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="32" t="s">
         <v>148</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>146</v>
       </c>
       <c r="D12" s="22" t="n">
         <v>4.15</v>
@@ -9357,15 +12281,15 @@
         <v>1.287</v>
       </c>
       <c r="K12" s="20" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="33" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D13" s="26" t="n">
         <v>5.99</v>
@@ -9389,15 +12313,15 @@
         <v>1.319</v>
       </c>
       <c r="K13" s="24" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="32" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D14" s="22" t="n">
         <v>6.68</v>
@@ -9421,15 +12345,15 @@
         <v>1.366</v>
       </c>
       <c r="K14" s="20" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D15" s="26" t="n">
         <v>2.55</v>
@@ -9453,15 +12377,15 @@
         <v>1.101</v>
       </c>
       <c r="K15" s="24" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="32" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D16" s="22" t="n">
         <v>1.83</v>
@@ -9485,15 +12409,15 @@
         <v>1.368</v>
       </c>
       <c r="K16" s="20" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D17" s="26" t="n">
         <v>1.08</v>
@@ -9517,15 +12441,15 @@
         <v>1.056</v>
       </c>
       <c r="K17" s="24" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="32" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D18" s="22" t="n">
         <v>32.04</v>
@@ -9549,15 +12473,15 @@
         <v>1.457</v>
       </c>
       <c r="K18" s="20" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="C19" s="33" t="s">
         <v>159</v>
-      </c>
-      <c r="C19" s="33" t="s">
-        <v>157</v>
       </c>
       <c r="D19" s="26" t="n">
         <v>11.25</v>
@@ -9581,7 +12505,7 @@
         <v>0.468</v>
       </c>
       <c r="K19" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -9626,12 +12550,12 @@
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="17" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
@@ -9641,12 +12565,12 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -9656,7 +12580,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -9666,51 +12590,51 @@
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="19" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J9" s="19" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L9" s="19" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="N9" s="19" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O9" s="19" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="32" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D10" s="22" t="n">
         <v>0.24</v>
@@ -9740,7 +12664,7 @@
         <v>0.632</v>
       </c>
       <c r="N10" s="39" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="O10" s="40" t="n">
         <v>31.5</v>
@@ -9748,10 +12672,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D11" s="26" t="n">
         <v>0.24</v>
@@ -9781,7 +12705,7 @@
         <v>0.654</v>
       </c>
       <c r="N11" s="39" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="O11" s="40" t="n">
         <v>52.5</v>
@@ -9789,10 +12713,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="32" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D12" s="22" t="n">
         <v>1.47</v>
@@ -9822,7 +12746,7 @@
         <v>0.613</v>
       </c>
       <c r="N12" s="39" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="O12" s="40" t="n">
         <v>16</v>
@@ -9830,10 +12754,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D13" s="26" t="n">
         <v>2.05</v>
@@ -9863,7 +12787,7 @@
         <v>0.267</v>
       </c>
       <c r="N13" s="39" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O13" s="40" t="n">
         <v>84.8</v>
@@ -9871,10 +12795,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="32" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D14" s="22" t="n">
         <v>0.62</v>
@@ -9904,7 +12828,7 @@
         <v>0.556</v>
       </c>
       <c r="N14" s="39" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="O14" s="40" t="n">
         <v>12</v>
@@ -9912,10 +12836,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D15" s="26" t="n">
         <v>0.17</v>
@@ -9945,7 +12869,7 @@
         <v>0.675</v>
       </c>
       <c r="N15" s="39" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O15" s="40" t="n">
         <v>3.2</v>
@@ -9953,10 +12877,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="32" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D16" s="22" t="n">
         <v>0.46</v>
@@ -9986,7 +12910,7 @@
         <v>0.733</v>
       </c>
       <c r="N16" s="39" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O16" s="40" t="n">
         <v>33.9</v>
@@ -9994,10 +12918,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D17" s="26" t="n">
         <v>0.68</v>
@@ -10027,7 +12951,7 @@
         <v>0.657</v>
       </c>
       <c r="N17" s="39" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O17" s="40" t="n">
         <v>43.3</v>
@@ -10035,10 +12959,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="32" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D18" s="22" t="n">
         <v>4.08</v>
@@ -10068,7 +12992,7 @@
         <v>0.391</v>
       </c>
       <c r="N18" s="39" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="O18" s="42" t="n">
         <v>18122.9</v>
@@ -10076,10 +13000,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="33" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D19" s="26" t="n">
         <v>2.04</v>
@@ -10109,7 +13033,7 @@
         <v>1.181</v>
       </c>
       <c r="N19" s="39" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O19" s="42" t="n">
         <v>63727.2</v>
@@ -10117,10 +13041,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="32" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D20" s="22" t="n">
         <v>1.34</v>
@@ -10152,10 +13076,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="33" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D21" s="26" t="n">
         <v>0.89</v>
@@ -10187,10 +13111,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="32" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D22" s="22" t="n">
         <v>2.33</v>
@@ -10222,10 +13146,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="33" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D23" s="26" t="n">
         <v>0.58</v>
@@ -10257,10 +13181,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="32" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C24" s="32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D24" s="22" t="n">
         <v>0.68</v>
@@ -10292,10 +13216,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="33" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D25" s="26" t="n">
         <v>0.87</v>
@@ -10327,10 +13251,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="32" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C26" s="32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D26" s="22" t="n">
         <v>4.02</v>
@@ -10362,10 +13286,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D27" s="26" t="n">
         <v>2.55</v>
@@ -10397,10 +13321,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="32" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C28" s="32" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D28" s="22" t="n">
         <v>1.83</v>
@@ -10432,10 +13356,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D29" s="26" t="n">
         <v>1.08</v>
@@ -10467,10 +13391,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="34" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D30" s="30" t="n">
         <v>2.15</v>
@@ -10502,10 +13426,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D31" s="26" t="n">
         <v>9.51</v>
@@ -10537,10 +13461,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="32" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C32" s="32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D32" s="22" t="n">
         <v>11.25</v>
@@ -10572,10 +13496,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D33" s="26" t="n">
         <v>32.04</v>
@@ -10607,10 +13531,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="32" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C34" s="32" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D34" s="22" t="n">
         <v>5.99</v>
@@ -10642,10 +13566,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D35" s="26" t="n">
         <v>4.15</v>
@@ -10677,10 +13601,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="32" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C36" s="32" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D36" s="22" t="n">
         <v>6.68</v>
@@ -10712,7 +13636,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="34" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C37" s="34"/>
       <c r="D37" s="30"/>
@@ -10774,135 +13698,135 @@
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="17" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="19" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="20" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C10" s="21" t="n">
         <v>51483.4291795651</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="24" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C11" s="25" t="n">
         <v>18162.8494728531</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="20" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C12" s="21" t="n">
         <v>18122.9</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="24" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C13" s="25" t="n">
         <v>63727.2</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="20" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C14" s="21" t="n">
         <v>163.645887585044</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="28" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C15" s="29" t="n">
         <f aca="false">C14/C10*100</f>
         <v>0.317861281178991</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="28" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C16" s="29" t="n">
         <f aca="false">C11/C10*100</f>
         <v>35.2790203805272</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="28" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C17" s="29" t="n">
         <f aca="false">C13/(C13+C12)*100</f>
         <v>77.8584265627043</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -10940,12 +13864,12 @@
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="17" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
@@ -10953,12 +13877,12 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -10966,7 +13890,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -10974,21 +13898,21 @@
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="19" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="32" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>14.1</v>
@@ -11002,7 +13926,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C11" s="27" t="n">
         <v>11.7</v>
@@ -11016,7 +13940,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="32" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>298.9</v>
@@ -11030,7 +13954,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C13" s="27" t="n">
         <v>204.5</v>
@@ -11044,7 +13968,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="32" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>91.3</v>
@@ -11058,7 +13982,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C15" s="27" t="n">
         <v>8.9</v>
@@ -11072,7 +13996,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="32" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C16" s="23" t="n">
         <v>44.7</v>
@@ -11086,7 +14010,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C17" s="27" t="n">
         <v>75.2</v>
@@ -11100,7 +14024,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="32" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>987.4</v>
@@ -11114,7 +14038,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="33" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C19" s="27" t="n">
         <v>217.2</v>
@@ -11128,7 +14052,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="32" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>143.6</v>
@@ -11142,7 +14066,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="33" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C21" s="27" t="n">
         <v>66.1</v>
@@ -11156,7 +14080,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="32" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C22" s="23" t="n">
         <v>278.1</v>
@@ -11170,7 +14094,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="33" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C23" s="27" t="n">
         <v>32.6</v>
@@ -11184,7 +14108,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="32" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C24" s="23" t="n">
         <v>146.4</v>
@@ -11198,7 +14122,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="33" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C25" s="27" t="n">
         <v>97.1</v>
@@ -11212,7 +14136,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="32" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C26" s="23" t="n">
         <v>173.2</v>
@@ -11226,7 +14150,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C27" s="27" t="n">
         <v>311.3</v>
@@ -11240,7 +14164,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="32" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C28" s="23" t="n">
         <v>268.2</v>
@@ -11254,7 +14178,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C29" s="27" t="n">
         <v>108.6</v>
@@ -11268,7 +14192,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="32" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C30" s="23" t="n">
         <v>2345.9</v>
@@ -11282,7 +14206,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="33" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C31" s="27" t="n">
         <v>2669.2</v>
@@ -11296,7 +14220,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="32" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C32" s="23" t="n">
         <v>6845.2</v>
@@ -11310,7 +14234,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="33" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C33" s="27" t="n">
         <v>1109.2</v>
@@ -11324,7 +14248,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="32" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C34" s="23" t="n">
         <v>624.6</v>
@@ -11338,7 +14262,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C35" s="27" t="n">
         <v>949.6</v>
@@ -11352,7 +14276,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="34" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C36" s="31" t="n">
         <f aca="false">C30+C31+C32</f>
@@ -11369,7 +14293,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="34" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C37" s="31" t="n">
         <f aca="false">C31+C32</f>
@@ -11422,12 +14346,12 @@
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="17" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
@@ -11438,12 +14362,12 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -11454,7 +14378,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -11465,33 +14389,33 @@
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="19" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="34" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D10" s="30" t="n">
         <v>62.28</v>
@@ -11511,10 +14435,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="33" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D11" s="26" t="n">
         <v>10.63</v>
@@ -11534,10 +14458,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="32" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D12" s="22" t="n">
         <v>6.25</v>
@@ -11557,10 +14481,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="33" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D13" s="26" t="n">
         <v>4.85</v>
@@ -11580,10 +14504,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="32" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D14" s="22" t="n">
         <v>4.42</v>
@@ -11603,10 +14527,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="33" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D15" s="26" t="n">
         <v>4.11</v>
@@ -11626,10 +14550,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="32" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D16" s="22" t="n">
         <v>2.14</v>
@@ -11649,10 +14573,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="33" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D17" s="26" t="n">
         <v>1.93</v>
@@ -11672,10 +14596,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="32" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D18" s="22" t="n">
         <v>1.85</v>
@@ -11695,10 +14619,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="33" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D19" s="26" t="n">
         <v>1.54</v>
@@ -11718,29 +14642,29 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="19" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="44" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C24" s="44" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D24" s="45" t="n">
         <v>65985.4</v>

--- a/auditoria/auditoria_dados_es.xlsx
+++ b/auditoria/auditoria_dados_es.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="836">
   <si>
     <t xml:space="preserve">Auditoria dos dados do artigo</t>
   </si>
@@ -1392,7 +1392,7 @@
     <t xml:space="preserve">A aba 12 pergunta se o número publicado bate com o CSV; esta pergunta se o indicador usado sustenta o que a frase afirma — são coisas diferentes. Os critérios saem do protocolo que o repositório já pratica (AUDITORIA.md B1–B6, AUDITORIA_HARD.md §0–§5, os gates INTEGRITY, os achados F1–F8 do parecer matemático); quatro são externos, acrescentados porque o protocolo interno não os cobre, e vêm marcados como tal na coluna Origem.</t>
   </si>
   <si>
-    <t xml:space="preserve">•  30 das 47 afirmações passam sem ressalva; 14 têm ressalva declarada longe do número; 3 pedem revisão.</t>
+    <t xml:space="preserve">•  39 das 47 afirmações passam sem ressalva; 4 têm ressalva declarada longe do número; 4 pedem revisão.</t>
   </si>
   <si>
     <t xml:space="preserve">•  Nenhum achado corrompe número publicado. O de maior consequência é o M — teste prometido em nota de rodapé e nunca executado, pela regra do próprio repositório.</t>
@@ -1497,169 +1497,169 @@
     <t xml:space="preserve">Oosterhaven (1988); Dietzenbacher (1997) — ausente em todo o repositório</t>
   </si>
   <si>
+    <t xml:space="preserve">aplicado: o Apêndice A.4 agora declara que a leitura causal do modelo oferta-dirigido é contestada e que os índices para frente descrevem posição, não impacto. Achado N fechado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipo II é limite inferior do induzido local</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVIEW_THEORIST_TOOLBOX.md:55 (F6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o Apêndice A.1 traz o argumento de monotonicidade pela série de Neumann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duas agregações legítimas do mesmo fluxo exigem nota de reconciliação, nunca escolha silenciosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUDITORIA.md:58 · REVIEW_CARACTERIZACAO.md:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quatro precedentes no repo; o Apêndice B.2 concilia 24,9 / 22,9 / 22,8 / 27,4 e a nota da Tabela 5 concilia 90,9 com 91,6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preços correntes: oscilação anual em setor sensível a preço é efeito nominal, não estrutural</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESULTADOS_CARACTERIZACAO.md:151 · DEEP_RESEARCH_PANORAMA.md:81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">declarado na Limitação (ii) E no ponto de uso, no parágrafo da siderurgia em §5. A deflação da série segue pendente como agenda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CILQ sem correção FLQ subestima o vazamento: o valor é limite inferior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVISAO_LITERATURA_IIOAS.md:63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~ RESSALVA FORA DO PONTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">declarado na Limitação (iii) como 'ordens de grandeza', mas não no ponto dos LQ de 2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A conclusão precisa ser invariante à convenção de spillover/feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_reconciliacao.py:70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o Apêndice B.3 reporta a banda 0,15–0,32% em quatro convenções alternativas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extração hipotética: declarar a especificação da injeção no ponto do número</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVIEW_FULL_MODE_V2.md:102 (R1-W3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o Apêndice A.7 declara que a injeção é a demanda final intra-estadual; o §6, onde os 13,0% aparecem, não repete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ligações puras são largamente tamanho: reportar junto com Rasmussen-Hirschman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17_caracterizacao_es_2008.py:88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nota de rodapé no §4 com o Pearson 0,96, agora auditável na aba 02 pela coluna VBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modelo nulo é ajuste descritivo, sem pretensão inferencial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVIEW_THEORIST_TOOLBOX.md:67 (F8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n/a nesta revisão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o apêndice de escores-z saiu da revisão final; nenhuma afirmação auditada depende dele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cruzamento entre safras e agregações exige rótulo explícito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEEP_RESEARCH_PANORAMA.md:264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 / 35 / 68 setores e as safras 2008 / 2015 / 2010–2021 são declarados em §3.1 e nas Limitações (ii) e (iii)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todo número publicado precisa de artefato persistido, não de stdout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVIEW_THEORIST_TOOLBOX.md:42 (F4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o Apêndice A.3 agora declara explicitamente que a igualdade com Miyazawa é identidade algébrica, não cálculo independente — não reivindica verificação que não existe. Achado L: ver ROTEIRO_PENDENCIAS.md se as matrizes chegarem e Miyazawa vier a ser computado de fato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teste prometido e não rodado conta como teste falhando</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVIEW_THEORIST_TOOLBOX.md:14 (F1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a nota do §4 não promete mais o teste; declara o ranking condicional ao rótulo adotado. Achado M: a reestimação em si permanece no ROTEIRO_PENDENCIAS.md, aguardando as matrizes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentuais calculados sobre os valores, não soma de parcelas arredondadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">esta pasta, aba 03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">corrigido nesta edição: somar a coluna de % do CSV dava um TOTAL de 100,01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O CSV persistido precisa ser internamente coerente em unidade</t>
+  </si>
+  <si>
     <t xml:space="preserve">⚑ REVISAR</t>
   </si>
   <si>
-    <t xml:space="preserve">o artigo diz 'pelo lado da oferta' (§3 e Apêndice A.4), mas em nenhum ponto registra que a leitura causal do modelo é contestada. Ver achado N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipo II é limite inferior do induzido local</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REVIEW_THEORIST_TOOLBOX.md:55 (F6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">o Apêndice A.1 traz o argumento de monotonicidade pela série de Neumann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duas agregações legítimas do mesmo fluxo exigem nota de reconciliação, nunca escolha silenciosa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUDITORIA.md:58 · REVIEW_CARACTERIZACAO.md:21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">quatro precedentes no repo; o Apêndice B.2 concilia 24,9 / 22,9 / 22,8 / 27,4 e a nota da Tabela 5 concilia 90,9 com 91,6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preços correntes: oscilação anual em setor sensível a preço é efeito nominal, não estrutural</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESULTADOS_CARACTERIZACAO.md:151 · DEEP_RESEARCH_PANORAMA.md:81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">declarado na Limitação (ii) E no ponto de uso, no parágrafo da siderurgia em §5. A deflação da série segue pendente como agenda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CILQ sem correção FLQ subestima o vazamento: o valor é limite inferior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REVISAO_LITERATURA_IIOAS.md:63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~ RESSALVA FORA DO PONTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">declarado na Limitação (iii) como 'ordens de grandeza', mas não no ponto dos LQ de 2015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A conclusão precisa ser invariante à convenção de spillover/feedback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06_reconciliacao.py:70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">o Apêndice B.3 reporta a banda 0,15–0,32% em quatro convenções alternativas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extração hipotética: declarar a especificação da injeção no ponto do número</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REVIEW_FULL_MODE_V2.md:102 (R1-W3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">o Apêndice A.7 declara que a injeção é a demanda final intra-estadual; o §6, onde os 13,0% aparecem, não repete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ligações puras são largamente tamanho: reportar junto com Rasmussen-Hirschman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17_caracterizacao_es_2008.py:88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nota de rodapé no §4 com o Pearson 0,96, agora auditável na aba 02 pela coluna VBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modelo nulo é ajuste descritivo, sem pretensão inferencial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REVIEW_THEORIST_TOOLBOX.md:67 (F8)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n/a nesta revisão</t>
-  </si>
-  <si>
-    <t xml:space="preserve">o apêndice de escores-z saiu da revisão final; nenhuma afirmação auditada depende dele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cruzamento entre safras e agregações exige rótulo explícito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEEP_RESEARCH_PANORAMA.md:264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 / 35 / 68 setores e as safras 2008 / 2015 / 2010–2021 são declarados em §3.1 e nas Limitações (ii) e (iii)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Todo número publicado precisa de artefato persistido, não de stdout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REVIEW_THEORIST_TOOLBOX.md:42 (F4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">falha em um caso: a decomposição de Miyazawa do Apêndice A.3 não é computada por nenhum script. Ver achado L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teste prometido e não rodado conta como teste falhando</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REVIEW_THEORIST_TOOLBOX.md:14 (F1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">falha em um caso: a reestimação do ranking de base sem Alimentos é prometida em nota de rodapé no §4 e nunca foi executada. Ver achado M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percentuais calculados sobre os valores, não soma de parcelas arredondadas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">esta pasta, aba 03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">corrigido nesta edição: somar a coluna de % do CSV dava um TOTAL de 100,01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O CSV persistido precisa ser internamente coerente em unidade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">falha: es_caracterizacao_2008.csv traz a mesma grandeza em duas unidades na mesma linha. Ver achado J</t>
+    <t xml:space="preserve">corrigido no código (17_caracterizacao_es_2008.py não grava mais ×1e6; 27_tab_multiplicadores.py detecta a escala pela invariante mult_emp_I≈emp_dir+emp_ind, testado nos dois formatos). O CSV em outputs/ ainda não foi regenerado — falta a matriz. Ver achado J e ROTEIRO_PENDENCIAS.md</t>
   </si>
   <si>
     <t xml:space="preserve">M20</t>
@@ -1680,7 +1680,7 @@
     <t xml:space="preserve">14_benchmark_ufs.py:42 vs 18_trajetoria_n68.py:56</t>
   </si>
   <si>
-    <t xml:space="preserve">falha: um script usa assert, o outro detecta a violação e faz pass. Ver achado K</t>
+    <t xml:space="preserve">corrigido: 18_trajetoria_n68.py agora usa assert no raio espectral (a condição correta; soma de coluna &lt;1 é suficiente, não necessária) e persiste as violações de coluna em outputs/diag_hawkins_n68.csv. Falta rodar com a pasta Nível 68 para saber se dispara em algum ano — achado K, ROTEIRO_PENDENCIAS.md</t>
   </si>
   <si>
     <t xml:space="preserve">M22</t>
@@ -1689,7 +1689,7 @@
     <t xml:space="preserve">A convenção do coeficiente de variação deve ser declarada</t>
   </si>
   <si>
-    <t xml:space="preserve">o CV publicado (0,16 / 0,28) é o populacional; o amostral daria 0,17 / 0,29. A escolha não está no texto. Ver achado S</t>
+    <t xml:space="preserve">aplicado: o Apêndice A.4 agora declara que o CV é o populacional. Achado S fechado</t>
   </si>
   <si>
     <t xml:space="preserve">Bloco 2 — as afirmações, uma a uma</t>
@@ -1728,7 +1728,7 @@
     <t xml:space="preserve">M8 · M19</t>
   </si>
   <si>
-    <t xml:space="preserve">o número publicado está certo, mas a coluna mult_emp_I do CSV está gravada ×1e6 e a coluna emp_dir_Rmi da mesma linha, não. Quem replicar pelo artefato erra por seis ordens de grandeza</t>
+    <t xml:space="preserve">número publicado correto; o código já foi corrigido (17_* não grava mais ×1e6; 27_tab_multiplicadores.py detecta a escala do CSV e produz a mesma tabela nos dois formatos, testado). O artefato em outputs/ ainda não foi regenerado — pendente das matrizes, ver ROTEIRO_PENDENCIAS.md (achado J)</t>
   </si>
   <si>
     <t xml:space="preserve">M7 · M19</t>
@@ -1737,7 +1737,7 @@
     <t xml:space="preserve">média simples, tipo II</t>
   </si>
   <si>
-    <t xml:space="preserve">mesma incoerência de unidade no artefato (achado J)</t>
+    <t xml:space="preserve">mesma situação: código corrigido, CSV pendente de regeneração (achado J)</t>
   </si>
   <si>
     <t xml:space="preserve">PTL padronizada pela média dos 26</t>
@@ -1761,7 +1761,7 @@
     <t xml:space="preserve">parcela do VBP nos setores rotulados base</t>
   </si>
   <si>
-    <t xml:space="preserve">o rótulo inclui Alimentos (22_benchmark_caracterizacao.py:18) e a nota de rodapé do §4 promete a reestimação sem Alimentos 'como checagem de replicação'. Enquanto ela não rodar, o '2º mais intensivo' é condicional ao rótulo. Redação sugerida: '2º mais intensivo em setores de base sob a classificação adotada, que inclui Alimentos'</t>
+    <t xml:space="preserve">o rótulo inclui Alimentos (22_benchmark_caracterizacao.py:18). A nota do §4 não promete mais o teste (M17 fechado no texto: a frase agora declara o ranking condicional ao rótulo adotado); a reestimação em si — se o ES continuaria 2º sem Alimentos — segue pendente das matrizes, ver ROTEIRO_PENDENCIAS.md (achado M)</t>
   </si>
   <si>
     <t xml:space="preserve">M8 · M15</t>
@@ -1815,7 +1815,7 @@
     <t xml:space="preserve">extração hipotética</t>
   </si>
   <si>
-    <t xml:space="preserve">a especificação da injeção (demanda final intra-estadual) está só no Apêndice A.7. Redação sugerida no §6: '...cairia 13,0% sob a injeção da demanda final intra-estadual'</t>
+    <t xml:space="preserve">aplicado: o §6 agora especifica no ponto de uso que a injeção é a demanda final intra-estadual, remetendo ao Apêndice A.7 — a ressalva deixou de estar só no apêndice</t>
   </si>
   <si>
     <t xml:space="preserve">M10 · M20</t>
@@ -1824,13 +1824,13 @@
     <t xml:space="preserve">quociente locacional, 2015</t>
   </si>
   <si>
-    <t xml:space="preserve">o LQ de 2015 vem da regionalização CILQ sem correção FLQ; a ressalva está na Limitação (iii)</t>
+    <t xml:space="preserve">aplicado: o §6 agora abre com a ressalva de que os LQ vêm da regionalização CILQ sem correção FLQ e indicam ordem, não nível exato — no mesmo parágrafo dos números, não só na Limitação (iii)</t>
   </si>
   <si>
     <t xml:space="preserve">idem</t>
   </si>
   <si>
-    <t xml:space="preserve">além da ressalva do CILQ: o texto diz 'rochas ornamentais' e o dado é 'Minerais não-metálicos'. Ver achado T</t>
+    <t xml:space="preserve">idem, mais o achado T: o texto diz 'rochas ornamentais' e o dado é 'Minerais não-metálicos'. Ver achado T</t>
   </si>
   <si>
     <t xml:space="preserve">M9 · M15 · M21</t>
@@ -1839,7 +1839,7 @@
     <t xml:space="preserve">ligação de Leontief, série nacional</t>
   </si>
   <si>
-    <t xml:space="preserve">preços correntes (Limitação ii) e o script do panorama detecta violação de Hawkins-Simon sem agir (achado K). A tendência de 12 anos é robusta ao efeito nominal; o nível de um ano, não</t>
+    <t xml:space="preserve">preços correntes (ressalva na Limitação ii, não no ponto). A guarda de Hawkins-Simon do script foi corrigida (achado K: assert no raio espectral); falta rodar com o Nível 68 para saber se algum ano viola, ver ROTEIRO_PENDENCIAS.md. A tendência de 12 anos é robusta ao efeito nominal; o nível de um ano, não</t>
   </si>
   <si>
     <t xml:space="preserve">M9 · M21</t>
@@ -1860,7 +1860,7 @@
     <t xml:space="preserve">ligação de Ghosh</t>
   </si>
   <si>
-    <t xml:space="preserve">o número confere, mas sustenta a leitura de 'fornecedora a montante'. Por M6, a ligação de Ghosh mede posição, não impacto — a frase do §4 não deve ser lida como previsão de efeito</t>
+    <t xml:space="preserve">o número confere e sustenta a leitura de 'fornecedora a montante'. Aplicado: o Apêndice A.4 agora declara que a ligação de Ghosh mede posição, não impacto — a frase do §4 deve ser lida sob essa ressalva metodológica</t>
   </si>
   <si>
     <t xml:space="preserve">ligação de Leontief</t>
@@ -1869,13 +1869,13 @@
     <t xml:space="preserve">CV populacional das ligações</t>
   </si>
   <si>
-    <t xml:space="preserve">o CV é o populacional; declarar qual, já que o amostral daria 0,17</t>
+    <t xml:space="preserve">aplicado: o Apêndice A.4 agora declara que o CV é o populacional (o amostral daria 0,17)</t>
   </si>
   <si>
     <t xml:space="preserve">M6 · M22</t>
   </si>
   <si>
-    <t xml:space="preserve">idem, e a ligação a frente é de Ghosh (M6): o amostral daria 0,29</t>
+    <t xml:space="preserve">idem, e a ligação a frente é de Ghosh (M6, também aplicado): o amostral daria 0,29</t>
   </si>
   <si>
     <t xml:space="preserve">M13 · M16</t>
@@ -1923,148 +1923,160 @@
     <t xml:space="preserve">Não — os números publicados dividem por 1e6 corretamente</t>
   </si>
   <si>
-    <t xml:space="preserve">Gravar já por R$ 1 milhão, ou renomear a coluna para explicitar o fator</t>
+    <t xml:space="preserve">17_caracterizacao_es_2008.py corrigido (não grava mais ×1e6) e 27_tab_multiplicadores.py agora detecta a escala do CSV pela invariante mult_emp_I≈emp_dir+emp_ind, testado nos dois formatos — produz a mesma Tabela 1 antes e depois da regeneração</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APLICADO no código; regeneração do CSV pendente da matriz MIP-ES-BR (2008).xlsx, ver ROTEIRO_PENDENCIAS.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18_trajetoria_n68.py:56-58 detecta soma de coluna de A ≥ 1 e executa pass; 14_benchmark_ufs.py:42 usa assert para a mesma checagem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indeterminado — UNVERIFIABLE_ACCESS: as matrizes do Nível 68 não estão no repositório, não é possível saber se a violação dispara em algum ano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guarda uniformizada pela condição correta (ΣA&lt;1 é suficiente, não necessária): assert no raio espectral, mais outputs/diag_hawkins_n68.csv registrando violações de coluna por ano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APLICADO no código; execução pendente da pasta Nível 68 (12 arquivos), ver ROTEIRO_PENDENCIAS.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A decomposição de Miyazawa do Apêndice A.3 não é computada por nenhum script (varredura em *.py: zero ocorrências); a cadeia número→artefato fecha por identidade algébrica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não — o valor é o feedback já verificado, por identidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O Apêndice A.3 agora declara explicitamente que a igualdade é identidade algébrica, não cálculo independente — não reivindica verificação inexistente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APLICADO (declaração); computar Miyazawa de fato é opcional, ver ROTEIRO_PENDENCIAS.md se as matrizes chegarem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A reestimação do ranking de base excluindo Alimentos é prometida em nota de rodapé no §4 'como checagem de replicação' e nunca foi executada (DA-1, aberto desde a rodada 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">research-integrity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sim, condicionalmente — o '2º mais intensivo em base' (36,4%) e a mediana de 21,0 dependem do rótulo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A nota do §4 não promete mais o teste; declara o ranking condicional à classificação adotada, que inclui Alimentos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APLICADO (redação); a reestimação em si é a única pendência que pode mudar uma afirmação publicada — pendente da matriz MIP-26x26-BR-2008.xlsx, ver ROTEIRO_PENDENCIAS.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nenhum documento do repositório registra a crítica canônica ao modelo de Ghosh como oferta-dirigido; Ghosh entra apenas como 'a convenção correta' para a ligação a frente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">causal-identification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não — nenhum número muda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O Apêndice A.4 agora declara que a ligação a frente por Ghosh mede posição na cadeia, e que a leitura do modelo como oferta-dirigido é contestada na literatura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APLICADO nesta edição</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duas referências de proveniência desta pasta apontavam para lugares inexistentes: 'AUDITORIA.md §B7' (seção nunca escrita) e uma nota CILQ em dados/README.md (25 linhas, não a contém)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🟡 Menor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">citation-hygiene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reapontadas para AUDITORIA.md B1–B6 e RESULTADOS_RQ_AB.md:103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">src/io_core.py não é importado por nenhum script (zero imports), mas README.md:47 e dados/README.md:11 o apresentam como funções-núcleo usadas pelo pipeline. Cobre parte da bateria: sem tipo II, ligações puras, extração hipotética, Miyazawa, LQ/HHI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Os dois README agora descrevem io_core.py como implementação de referência, não usada pelo pipeline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dados/README.md descreve o pipeline como '01–13' quando o artigo depende de 14 a 27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faixa atualizada para 01–28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O protocolo B7 é invocado pelo nome e usado, mas nunca foi definido em nenhum .md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escrito em AUDITORIA.md: verificação de metadados das referências que sustentam números, com o vocabulário VERIFICADA / CORRIGIDA / UNVERIFIABLE_ACCESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O coeficiente de variação publicado (0,16 / 0,28) é o populacional; o amostral daria 0,17 / 0,29. A convenção não está declarada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🟢 Cosmético</t>
+  </si>
+  <si>
+    <t xml:space="preserve">writing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O Apêndice A.4 agora declara que o CV é o populacional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O texto diz 'rochas ornamentais no Central Sul' e o setor correspondente no dado é 'Minerais não-metálicos' (LQ 7,687)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nota de equivalência — já registrada na aba 09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tensão no cânone interno: DEEP_RESEARCH_CARACTERIZACAO.md:60 diz que as ligações puras corrigem o viés de Rasmussen-Hirschman por não pesar tamanho; a Limitação (iv) diz que elas favorecem setores grandes. As duas leituras são defensáveis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🟢 Declarado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nenhuma ação necessária; registrado para o caso de o parecerista notar</t>
   </si>
   <si>
     <t xml:space="preserve">ABERTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18_trajetoria_n68.py:56-58 detecta soma de coluna de A ≥ 1 e executa pass; 14_benchmark_ufs.py:42 usa assert para a mesma checagem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indeterminado — UNVERIFIABLE_ACCESS: as matrizes do Nível 68 não estão no repositório, não é possível saber se a violação dispara em algum ano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trocar pass por assert, ou registrar em CSV quais anos violam e o raio espectral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A decomposição de Miyazawa do Apêndice A.3 não é computada por nenhum script (varredura em *.py: zero ocorrências); a cadeia número→artefato fecha por identidade algébrica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não — o valor é o feedback já verificado, por identidade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ou um script que compute Δ_LL e persista o CSV, ou uma frase no apêndice dizendo que o resultado é identidade algébrica e não cálculo independente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A reestimação do ranking de base excluindo Alimentos é prometida em nota de rodapé no §4 'como checagem de replicação' e nunca foi executada (DA-1, aberto desde a rodada 3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">research-integrity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sim, condicionalmente — o '2º mais intensivo em base' (36,4%) e a mediana de 21,0 dependem do rótulo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rodar 22_* e 10_* sem Alimentos e reportar o novo ranking, ou retirar a promessa da nota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nenhum documento do repositório registra a crítica canônica ao modelo de Ghosh como oferta-dirigido; Ghosh entra apenas como 'a convenção correta' para a ligação a frente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">causal-identification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não — nenhum número muda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meia frase no Apêndice A.4: a ligação a frente por Ghosh mede posição na cadeia, e a leitura do modelo como oferta-dirigido é contestada na literatura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duas referências de proveniência desta pasta apontavam para lugares inexistentes: 'AUDITORIA.md §B7' (seção nunca escrita) e uma nota CILQ em dados/README.md (25 linhas, não a contém)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🟡 Menor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">citation-hygiene</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reapontadas para AUDITORIA.md B1–B6 e RESULTADOS_RQ_AB.md:103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APLICADO nesta edição</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">src/io_core.py não é importado por nenhum script (zero imports), mas README.md:47 e dados/README.md:11 o apresentam como funções-núcleo usadas pelo pipeline. Cobre parte da bateria: sem tipo II, ligações puras, extração hipotética, Miyazawa, LQ/HHI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrigir os dois README, ou passar a importá-lo de fato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dados/README.md descreve o pipeline como '01–13' quando o artigo depende de 14 a 27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atualizar a faixa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O protocolo B7 é invocado pelo nome e usado, mas nunca foi definido em nenhum .md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escrever B7 em AUDITORIA.md: verificação de metadados das referências que sustentam números, com o vocabulário VERIFICADA / CORRIGIDA / UNVERIFIABLE_ACCESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O coeficiente de variação publicado (0,16 / 0,28) é o populacional; o amostral daria 0,17 / 0,29. A convenção não está declarada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🟢 Cosmético</t>
-  </si>
-  <si>
-    <t xml:space="preserve">writing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uma palavra no Apêndice A.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O texto diz 'rochas ornamentais no Central Sul' e o setor correspondente no dado é 'Minerais não-metálicos' (LQ 7,687)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nota de equivalência — já registrada na aba 09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tensão no cânone interno: DEEP_RESEARCH_CARACTERIZACAO.md:60 diz que as ligações puras corrigem o viés de Rasmussen-Hirschman por não pesar tamanho; a Limitação (iv) diz que elas favorecem setores grandes. As duas leituras são defensáveis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🟢 Declarado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nenhuma ação necessária; registrado para o caso de o parecerista notar</t>
   </si>
   <si>
     <t xml:space="preserve">V</t>
@@ -7098,7 +7110,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="33" t="s">
         <v>482</v>
       </c>
@@ -7112,258 +7124,258 @@
         <v>485</v>
       </c>
       <c r="F15" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="G15" s="24" t="s">
         <v>486</v>
-      </c>
-      <c r="G15" s="24" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="32" t="s">
+        <v>487</v>
+      </c>
+      <c r="C16" s="20" t="s">
         <v>488</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>489</v>
       </c>
       <c r="D16" s="32" t="s">
         <v>462</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F16" s="32" t="s">
         <v>464</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="33" t="s">
+        <v>491</v>
+      </c>
+      <c r="C17" s="24" t="s">
         <v>492</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>493</v>
       </c>
       <c r="D17" s="33" t="s">
         <v>462</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F17" s="33" t="s">
         <v>464</v>
       </c>
       <c r="G17" s="24" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="32" t="s">
+        <v>495</v>
+      </c>
+      <c r="C18" s="20" t="s">
         <v>496</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>497</v>
       </c>
       <c r="D18" s="32" t="s">
         <v>462</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F18" s="32" t="s">
         <v>464</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="33" t="s">
+        <v>499</v>
+      </c>
+      <c r="C19" s="24" t="s">
         <v>500</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>501</v>
       </c>
       <c r="D19" s="33" t="s">
         <v>462</v>
       </c>
       <c r="E19" s="24" t="s">
+        <v>501</v>
+      </c>
+      <c r="F19" s="33" t="s">
         <v>502</v>
       </c>
-      <c r="F19" s="33" t="s">
+      <c r="G19" s="24" t="s">
         <v>503</v>
-      </c>
-      <c r="G19" s="24" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="32" t="s">
+        <v>504</v>
+      </c>
+      <c r="C20" s="20" t="s">
         <v>505</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>506</v>
       </c>
       <c r="D20" s="32" t="s">
         <v>462</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F20" s="32" t="s">
         <v>464</v>
       </c>
       <c r="G20" s="20" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="33" t="s">
+        <v>508</v>
+      </c>
+      <c r="C21" s="24" t="s">
         <v>509</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>510</v>
       </c>
       <c r="D21" s="33" t="s">
         <v>462</v>
       </c>
       <c r="E21" s="24" t="s">
+        <v>510</v>
+      </c>
+      <c r="F21" s="33" t="s">
+        <v>502</v>
+      </c>
+      <c r="G21" s="24" t="s">
         <v>511</v>
-      </c>
-      <c r="F21" s="33" t="s">
-        <v>503</v>
-      </c>
-      <c r="G21" s="24" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="32" t="s">
+        <v>512</v>
+      </c>
+      <c r="C22" s="20" t="s">
         <v>513</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>514</v>
       </c>
       <c r="D22" s="32" t="s">
         <v>462</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F22" s="32" t="s">
         <v>464</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="33" t="s">
+        <v>516</v>
+      </c>
+      <c r="C23" s="24" t="s">
         <v>517</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>518</v>
       </c>
       <c r="D23" s="33" t="s">
         <v>462</v>
       </c>
       <c r="E23" s="24" t="s">
+        <v>518</v>
+      </c>
+      <c r="F23" s="33" t="s">
         <v>519</v>
       </c>
-      <c r="F23" s="33" t="s">
+      <c r="G23" s="24" t="s">
         <v>520</v>
-      </c>
-      <c r="G23" s="24" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="32" t="s">
+        <v>521</v>
+      </c>
+      <c r="C24" s="20" t="s">
         <v>522</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>523</v>
       </c>
       <c r="D24" s="32" t="s">
         <v>462</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F24" s="32" t="s">
         <v>464</v>
       </c>
       <c r="G24" s="20" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="33" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="33" t="s">
+      <c r="C25" s="24" t="s">
         <v>526</v>
-      </c>
-      <c r="C25" s="24" t="s">
-        <v>527</v>
       </c>
       <c r="D25" s="33" t="s">
         <v>462</v>
       </c>
       <c r="E25" s="24" t="s">
+        <v>527</v>
+      </c>
+      <c r="F25" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="G25" s="24" t="s">
         <v>528</v>
       </c>
-      <c r="F25" s="33" t="s">
-        <v>486</v>
-      </c>
-      <c r="G25" s="24" t="s">
+    </row>
+    <row r="26" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="32" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="32" t="s">
+      <c r="C26" s="20" t="s">
         <v>530</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>531</v>
       </c>
       <c r="D26" s="32" t="s">
         <v>462</v>
       </c>
       <c r="E26" s="20" t="s">
+        <v>531</v>
+      </c>
+      <c r="F26" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="G26" s="20" t="s">
         <v>532</v>
-      </c>
-      <c r="F26" s="32" t="s">
-        <v>486</v>
-      </c>
-      <c r="G26" s="20" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="33" t="s">
+        <v>533</v>
+      </c>
+      <c r="C27" s="24" t="s">
         <v>534</v>
-      </c>
-      <c r="C27" s="24" t="s">
-        <v>535</v>
       </c>
       <c r="D27" s="33" t="s">
         <v>462</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F27" s="33" t="s">
         <v>464</v>
       </c>
       <c r="G27" s="24" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="32" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="32" t="s">
+      <c r="C28" s="20" t="s">
         <v>538</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>539</v>
       </c>
       <c r="D28" s="32" t="s">
         <v>484</v>
@@ -7372,7 +7384,7 @@
         <v>114</v>
       </c>
       <c r="F28" s="32" t="s">
-        <v>486</v>
+        <v>539</v>
       </c>
       <c r="G28" s="20" t="s">
         <v>540</v>
@@ -7389,16 +7401,16 @@
         <v>462</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F29" s="33" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G29" s="24" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="32" t="s">
         <v>544</v>
       </c>
@@ -7412,7 +7424,7 @@
         <v>546</v>
       </c>
       <c r="F30" s="32" t="s">
-        <v>486</v>
+        <v>464</v>
       </c>
       <c r="G30" s="20" t="s">
         <v>547</v>
@@ -7432,7 +7444,7 @@
         <v>114</v>
       </c>
       <c r="F31" s="33" t="s">
-        <v>503</v>
+        <v>464</v>
       </c>
       <c r="G31" s="24" t="s">
         <v>550</v>
@@ -7474,7 +7486,7 @@
         <v>368</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E35" s="20" t="s">
         <v>555</v>
@@ -7495,7 +7507,7 @@
         <v>370</v>
       </c>
       <c r="D36" s="33" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E36" s="24" t="s">
         <v>556</v>
@@ -7623,7 +7635,7 @@
         <v>380</v>
       </c>
       <c r="D42" s="33" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E42" s="24" t="s">
         <v>561</v>
@@ -7636,7 +7648,7 @@
         <v>2.45</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="32" t="s">
         <v>377</v>
       </c>
@@ -7650,7 +7662,7 @@
         <v>560</v>
       </c>
       <c r="F43" s="32" t="s">
-        <v>503</v>
+        <v>539</v>
       </c>
       <c r="G43" s="20" t="s">
         <v>563</v>
@@ -7673,7 +7685,7 @@
         <v>565</v>
       </c>
       <c r="F44" s="33" t="s">
-        <v>503</v>
+        <v>539</v>
       </c>
       <c r="G44" s="24" t="s">
         <v>566</v>
@@ -7690,7 +7702,7 @@
         <v>384</v>
       </c>
       <c r="D45" s="32" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E45" s="20" t="s">
         <v>567</v>
@@ -7713,7 +7725,7 @@
         <v>386</v>
       </c>
       <c r="D46" s="33" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E46" s="24" t="s">
         <v>569</v>
@@ -7818,13 +7830,13 @@
         <v>395</v>
       </c>
       <c r="D51" s="32" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E51" s="20" t="s">
         <v>573</v>
       </c>
       <c r="F51" s="32" t="s">
-        <v>486</v>
+        <v>539</v>
       </c>
       <c r="G51" s="20" t="s">
         <v>574</v>
@@ -7906,7 +7918,7 @@
         <v>400</v>
       </c>
       <c r="D55" s="32" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E55" s="20" t="s">
         <v>580</v>
@@ -7929,13 +7941,13 @@
         <v>401</v>
       </c>
       <c r="D56" s="33" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E56" s="24" t="s">
         <v>582</v>
       </c>
       <c r="F56" s="33" t="s">
-        <v>486</v>
+        <v>539</v>
       </c>
       <c r="G56" s="24" t="s">
         <v>583</v>
@@ -7952,7 +7964,7 @@
         <v>403</v>
       </c>
       <c r="D57" s="32" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E57" s="20" t="s">
         <v>582</v>
@@ -7973,7 +7985,7 @@
         <v>404</v>
       </c>
       <c r="D58" s="33" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E58" s="24" t="s">
         <v>582</v>
@@ -7994,7 +8006,7 @@
         <v>405</v>
       </c>
       <c r="D59" s="32" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E59" s="20" t="s">
         <v>584</v>
@@ -8015,7 +8027,7 @@
         <v>407</v>
       </c>
       <c r="D60" s="33" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E60" s="24" t="s">
         <v>584</v>
@@ -8036,7 +8048,7 @@
         <v>215</v>
       </c>
       <c r="D61" s="32" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E61" s="20" t="s">
         <v>585</v>
@@ -8059,7 +8071,7 @@
         <v>411</v>
       </c>
       <c r="D62" s="33" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E62" s="24" t="s">
         <v>587</v>
@@ -8082,7 +8094,7 @@
         <v>413</v>
       </c>
       <c r="D63" s="32" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E63" s="20" t="s">
         <v>587</v>
@@ -8130,7 +8142,7 @@
         <v>591</v>
       </c>
       <c r="F65" s="32" t="s">
-        <v>503</v>
+        <v>464</v>
       </c>
       <c r="G65" s="20" t="s">
         <v>592</v>
@@ -8139,7 +8151,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="33" t="s">
         <v>416</v>
       </c>
@@ -8153,7 +8165,7 @@
         <v>594</v>
       </c>
       <c r="F66" s="33" t="s">
-        <v>503</v>
+        <v>464</v>
       </c>
       <c r="G66" s="24" t="s">
         <v>595</v>
@@ -8176,7 +8188,7 @@
         <v>594</v>
       </c>
       <c r="F67" s="32" t="s">
-        <v>503</v>
+        <v>464</v>
       </c>
       <c r="G67" s="20" t="s">
         <v>596</v>
@@ -8199,7 +8211,7 @@
         <v>594</v>
       </c>
       <c r="F68" s="33" t="s">
-        <v>503</v>
+        <v>464</v>
       </c>
       <c r="G68" s="24" t="s">
         <v>596</v>
@@ -8222,7 +8234,7 @@
         <v>594</v>
       </c>
       <c r="F69" s="32" t="s">
-        <v>503</v>
+        <v>464</v>
       </c>
       <c r="G69" s="20" t="s">
         <v>596</v>
@@ -8245,7 +8257,7 @@
         <v>594</v>
       </c>
       <c r="F70" s="33" t="s">
-        <v>503</v>
+        <v>464</v>
       </c>
       <c r="G70" s="24" t="s">
         <v>597</v>
@@ -8254,7 +8266,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="32" t="s">
         <v>429</v>
       </c>
@@ -8268,7 +8280,7 @@
         <v>599</v>
       </c>
       <c r="F71" s="32" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G71" s="20" t="s">
         <v>600</v>
@@ -8291,7 +8303,7 @@
         <v>599</v>
       </c>
       <c r="F72" s="33" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G72" s="24" t="s">
         <v>596</v>
@@ -8314,7 +8326,7 @@
         <v>602</v>
       </c>
       <c r="F73" s="32" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G73" s="20" t="s">
         <v>596</v>
@@ -8337,7 +8349,7 @@
         <v>602</v>
       </c>
       <c r="F74" s="33" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G74" s="24" t="s">
         <v>596</v>
@@ -8354,7 +8366,7 @@
         <v>437</v>
       </c>
       <c r="D75" s="32" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E75" s="20" t="s">
         <v>603</v>
@@ -8383,7 +8395,7 @@
         <v>606</v>
       </c>
       <c r="F76" s="33" t="s">
-        <v>486</v>
+        <v>464</v>
       </c>
       <c r="G76" s="24" t="s">
         <v>607</v>
@@ -8413,7 +8425,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="33" t="s">
         <v>383</v>
       </c>
@@ -8427,7 +8439,7 @@
         <v>609</v>
       </c>
       <c r="F78" s="33" t="s">
-        <v>503</v>
+        <v>464</v>
       </c>
       <c r="G78" s="24" t="s">
         <v>610</v>
@@ -8436,7 +8448,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="32" t="s">
         <v>383</v>
       </c>
@@ -8450,7 +8462,7 @@
         <v>609</v>
       </c>
       <c r="F79" s="32" t="s">
-        <v>503</v>
+        <v>464</v>
       </c>
       <c r="G79" s="20" t="s">
         <v>612</v>
@@ -8490,7 +8502,7 @@
         <v>217</v>
       </c>
       <c r="D81" s="32" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E81" s="20" t="s">
         <v>616</v>
@@ -8531,7 +8543,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="32" t="s">
         <v>623</v>
       </c>
@@ -8574,15 +8586,15 @@
         <v>633</v>
       </c>
       <c r="H86" s="33" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="32" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C87" s="20" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D87" s="32" t="s">
         <v>625</v>
@@ -8591,266 +8603,266 @@
         <v>626</v>
       </c>
       <c r="F87" s="20" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="G87" s="20" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H87" s="32" t="s">
-        <v>629</v>
+        <v>639</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="33" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C88" s="24" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="D88" s="33" t="s">
         <v>625</v>
       </c>
       <c r="E88" s="24" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="F88" s="24" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="G88" s="24" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="H88" s="33" t="s">
-        <v>629</v>
+        <v>645</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="32" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C89" s="20" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="D89" s="32" t="s">
         <v>625</v>
       </c>
       <c r="E89" s="20" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="F89" s="20" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="G89" s="20" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="H89" s="32" t="s">
-        <v>629</v>
+        <v>651</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="33" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="C90" s="24" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="D90" s="33" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="E90" s="24" t="s">
+        <v>655</v>
+      </c>
+      <c r="F90" s="24" t="s">
+        <v>656</v>
+      </c>
+      <c r="G90" s="24" t="s">
+        <v>657</v>
+      </c>
+      <c r="H90" s="33" t="s">
         <v>651</v>
-      </c>
-      <c r="F90" s="24" t="s">
-        <v>652</v>
-      </c>
-      <c r="G90" s="24" t="s">
-        <v>653</v>
-      </c>
-      <c r="H90" s="33" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="32" t="s">
+        <v>658</v>
+      </c>
+      <c r="C91" s="20" t="s">
+        <v>659</v>
+      </c>
+      <c r="D91" s="32" t="s">
+        <v>654</v>
+      </c>
+      <c r="E91" s="20" t="s">
         <v>655</v>
       </c>
-      <c r="C91" s="20" t="s">
+      <c r="F91" s="20" t="s">
         <v>656</v>
       </c>
-      <c r="D91" s="32" t="s">
-        <v>650</v>
-      </c>
-      <c r="E91" s="20" t="s">
+      <c r="G91" s="20" t="s">
+        <v>660</v>
+      </c>
+      <c r="H91" s="32" t="s">
         <v>651</v>
-      </c>
-      <c r="F91" s="20" t="s">
-        <v>652</v>
-      </c>
-      <c r="G91" s="20" t="s">
-        <v>657</v>
-      </c>
-      <c r="H91" s="32" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="33" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C92" s="24" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="D92" s="33" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="E92" s="24" t="s">
+        <v>655</v>
+      </c>
+      <c r="F92" s="24" t="s">
+        <v>656</v>
+      </c>
+      <c r="G92" s="24" t="s">
+        <v>663</v>
+      </c>
+      <c r="H92" s="33" t="s">
         <v>651</v>
-      </c>
-      <c r="F92" s="24" t="s">
-        <v>652</v>
-      </c>
-      <c r="G92" s="24" t="s">
-        <v>660</v>
-      </c>
-      <c r="H92" s="33" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="32" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="C93" s="20" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="D93" s="32" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="E93" s="20" t="s">
         <v>626</v>
       </c>
       <c r="F93" s="20" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="G93" s="20" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="H93" s="32" t="s">
-        <v>629</v>
+        <v>651</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="33" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="C94" s="24" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="D94" s="33" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="E94" s="24" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="F94" s="24" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="G94" s="24" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="H94" s="33" t="s">
-        <v>629</v>
+        <v>651</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="32" t="s">
+        <v>672</v>
+      </c>
+      <c r="C95" s="20" t="s">
+        <v>673</v>
+      </c>
+      <c r="D95" s="32" t="s">
         <v>669</v>
       </c>
-      <c r="C95" s="20" t="s">
+      <c r="E95" s="20" t="s">
         <v>670</v>
       </c>
-      <c r="D95" s="32" t="s">
-        <v>666</v>
-      </c>
-      <c r="E95" s="20" t="s">
-        <v>667</v>
-      </c>
       <c r="F95" s="20" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="G95" s="20" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="H95" s="32" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B96" s="33" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="C96" s="24" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="D96" s="33" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="E96" s="24" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="F96" s="24" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="G96" s="24" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="H96" s="33" t="s">
-        <v>629</v>
+        <v>679</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B97" s="32" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="C97" s="20" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="D97" s="32" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="E97" s="20" t="s">
         <v>626</v>
       </c>
       <c r="F97" s="20" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="G97" s="20" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="H97" s="32" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B98" s="33" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="C98" s="24" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="D98" s="33" t="s">
         <v>625</v>
       </c>
       <c r="E98" s="24" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="F98" s="24" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="G98" s="24" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="H98" s="33" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
     </row>
   </sheetData>
@@ -8892,119 +8904,119 @@
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="17" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="19" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="20" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="24" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="20" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="24" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C10" s="24" t="s">
+        <v>701</v>
+      </c>
+      <c r="D10" s="24" t="s">
         <v>697</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="20" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="24" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="20" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="24" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="20" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
     </row>
   </sheetData>
@@ -9040,12 +9052,12 @@
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="17" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
@@ -9053,10 +9065,10 @@
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="19" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>458</v>
@@ -9067,100 +9079,100 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="20" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="24" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="20" t="s">
+        <v>727</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>728</v>
+      </c>
+      <c r="D9" s="20" t="s">
         <v>723</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="E9" s="20" t="s">
         <v>724</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>719</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="24" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="20" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="24" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="20" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
     </row>
   </sheetData>
@@ -9201,7 +9213,7 @@
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="17" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
@@ -9223,128 +9235,128 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="32" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="33" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="C8" s="24" t="s">
         <v>625</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="32" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="C9" s="20" t="s">
         <v>625</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="33" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="C10" s="24" t="s">
         <v>625</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="32" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="33" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="32" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="33" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="32" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="C15" s="20" t="s">
         <v>625</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
     </row>
   </sheetData>
@@ -9379,256 +9391,256 @@
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="17" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="19" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="20" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="24" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="20" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="24" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="20" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="24" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="20" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="24" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="20" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="24" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="20" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="24" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="20" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="24" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="20" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="24" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="20" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="24" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="20" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="24" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="20" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
     </row>
   </sheetData>
